--- a/Excel/DateFunctions8001.xlsx
+++ b/Excel/DateFunctions8001.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8D37F67-F7B7-41C1-9C75-F4D9776C189D}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA22EFCF-0C0A-4B27-BA89-F009E9291851}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="2" xr2:uid="{FFAF0F3A-FACC-44CD-90E3-6CA7DF844403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="4" xr2:uid="{FFAF0F3A-FACC-44CD-90E3-6CA7DF844403}"/>
   </bookViews>
   <sheets>
     <sheet name="Today" sheetId="1" r:id="rId1"/>
     <sheet name="Now" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="YearMonthDay" sheetId="3" r:id="rId3"/>
+    <sheet name="EDate" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet4" sheetId="6" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">YearMonthDay!$A$1:$E$54</definedName>
+  </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
   <si>
     <t>EmployeeNam</t>
   </si>
@@ -207,16 +212,113 @@
   </si>
   <si>
     <t>Thaskira MD</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Bollu Pavan Kumar</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>find out the people list who born in 2003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">give me the month wise count of the people </t>
+  </si>
+  <si>
+    <t>give me the date where most of my company employee are born</t>
+  </si>
+  <si>
+    <t>Sample Questions</t>
+  </si>
+  <si>
+    <t>Expected Delivary Date</t>
+  </si>
+  <si>
+    <t>Item Name</t>
+  </si>
+  <si>
+    <t>Order Date</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Office Chair</t>
+  </si>
+  <si>
+    <t>Mobile Phone</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t>Desk Lamp</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Keyboard</t>
+  </si>
+  <si>
+    <t>Air Conditioner</t>
+  </si>
+  <si>
+    <t>Coffee Machine</t>
+  </si>
+  <si>
+    <t>Bookshelf</t>
+  </si>
+  <si>
+    <t>Days takes to deliver</t>
+  </si>
+  <si>
+    <t>Months takes to deliver</t>
+  </si>
+  <si>
+    <t>Years takes to deliver</t>
+  </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>Days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculate how many years the person </t>
+  </si>
+  <si>
+    <t>calculate total months of the peron life</t>
+  </si>
+  <si>
+    <t>calculate total days of the peron life</t>
+  </si>
+  <si>
+    <t>display the age in the following format</t>
+  </si>
+  <si>
+    <t>24 years 2 month 1 day old</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="169" formatCode="[$-409]d/mmm/yy;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,8 +345,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -257,8 +373,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -309,11 +437,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -334,6 +471,35 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -748,7 +914,7 @@
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="6">
         <f ca="1">NOW()</f>
-        <v>46294.473957870374</v>
+        <v>46294.532499652778</v>
       </c>
     </row>
   </sheetData>
@@ -758,603 +924,1107 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D35901-0459-40DA-9AE9-B07B971850EC}">
-  <dimension ref="A1:E884"/>
+  <dimension ref="A1:G885"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7265625" style="2"/>
+    <col min="7" max="7" width="55.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-    </row>
-    <row r="2" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C1" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="12">
+        <v>37925</v>
+      </c>
+      <c r="C2" s="15">
+        <f>YEAR(B2)</f>
+        <v>2003</v>
+      </c>
+      <c r="D2" s="13">
+        <f>MONTH(B2)</f>
+        <v>10</v>
+      </c>
+      <c r="E2" s="15">
+        <f>DAY(B2)</f>
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="12">
+        <v>37195</v>
+      </c>
+      <c r="C3" s="15">
+        <f>YEAR(B3)</f>
+        <v>2001</v>
+      </c>
+      <c r="D3" s="13">
+        <f>MONTH(B3)</f>
+        <v>10</v>
+      </c>
+      <c r="E3" s="15">
+        <f>DAY(B3)</f>
+        <v>31</v>
+      </c>
+      <c r="G3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B4" s="12">
         <v>37832</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-    </row>
-    <row r="3" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="C4" s="15">
+        <f>YEAR(B4)</f>
+        <v>2003</v>
+      </c>
+      <c r="D4" s="13">
+        <f>MONTH(B4)</f>
+        <v>7</v>
+      </c>
+      <c r="E4" s="15">
+        <f>DAY(B4)</f>
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="12">
+        <v>37710</v>
+      </c>
+      <c r="C5" s="15">
+        <f>YEAR(B5)</f>
+        <v>2003</v>
+      </c>
+      <c r="D5" s="13">
+        <f>MONTH(B5)</f>
+        <v>3</v>
+      </c>
+      <c r="E5" s="15">
+        <f>DAY(B5)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="12">
+        <v>38290</v>
+      </c>
+      <c r="C6" s="15">
+        <f>YEAR(B6)</f>
+        <v>2004</v>
+      </c>
+      <c r="D6" s="13">
+        <f>MONTH(B6)</f>
+        <v>10</v>
+      </c>
+      <c r="E6" s="15">
+        <f>DAY(B6)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="12">
+        <v>38351</v>
+      </c>
+      <c r="C7" s="15">
+        <f>YEAR(B7)</f>
+        <v>2004</v>
+      </c>
+      <c r="D7" s="13">
+        <f>MONTH(B7)</f>
+        <v>12</v>
+      </c>
+      <c r="E7" s="15">
+        <f>DAY(B7)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="12">
+        <v>37893</v>
+      </c>
+      <c r="C8" s="15">
+        <f>YEAR(B8)</f>
+        <v>2003</v>
+      </c>
+      <c r="D8" s="13">
+        <f>MONTH(B8)</f>
         <v>9</v>
       </c>
-      <c r="B3" s="12">
-        <v>38296</v>
-      </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="12">
-        <v>37442</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-    </row>
-    <row r="5" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="12">
-        <v>38428</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-    </row>
-    <row r="6" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="E8" s="15">
+        <f>DAY(B8)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="12">
+        <v>38349</v>
+      </c>
+      <c r="C9" s="15">
+        <f>YEAR(B9)</f>
+        <v>2004</v>
+      </c>
+      <c r="D9" s="13">
+        <f>MONTH(B9)</f>
         <v>12</v>
       </c>
-      <c r="B6" s="12">
-        <v>37714</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-    </row>
-    <row r="7" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="12">
-        <v>37965</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-    </row>
-    <row r="8" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="E9" s="15">
+        <f>DAY(B9)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="12">
+        <v>37283</v>
+      </c>
+      <c r="C10" s="15">
+        <f>YEAR(B10)</f>
+        <v>2002</v>
+      </c>
+      <c r="D10" s="13">
+        <f>MONTH(B10)</f>
+        <v>1</v>
+      </c>
+      <c r="E10" s="15">
+        <f>DAY(B10)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="12">
+        <v>38408</v>
+      </c>
+      <c r="C11" s="15">
+        <f>YEAR(B11)</f>
+        <v>2005</v>
+      </c>
+      <c r="D11" s="13">
+        <f>MONTH(B11)</f>
+        <v>2</v>
+      </c>
+      <c r="E11" s="15">
+        <f>DAY(B11)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B12" s="12">
         <v>37704</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-    </row>
-    <row r="9" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="12">
-        <v>38408</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-    </row>
-    <row r="10" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="12">
-        <v>38275</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="12">
-        <v>37997</v>
-      </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-    </row>
-    <row r="12" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="12">
-        <v>37710</v>
-      </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-    </row>
-    <row r="13" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="C12" s="15">
+        <f>YEAR(B12)</f>
+        <v>2003</v>
+      </c>
+      <c r="D12" s="13">
+        <f>MONTH(B12)</f>
+        <v>3</v>
+      </c>
+      <c r="E12" s="15">
+        <f>DAY(B12)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="12">
-        <v>37748</v>
-      </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-    </row>
-    <row r="14" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+        <v>37826</v>
+      </c>
+      <c r="C13" s="15">
+        <f>YEAR(B13)</f>
+        <v>2003</v>
+      </c>
+      <c r="D13" s="13">
+        <f>MONTH(B13)</f>
+        <v>7</v>
+      </c>
+      <c r="E13" s="15">
+        <f>DAY(B13)</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B14" s="12">
-        <v>37826</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
-    </row>
-    <row r="15" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+        <v>37126</v>
+      </c>
+      <c r="C14" s="15">
+        <f>YEAR(B14)</f>
+        <v>2001</v>
+      </c>
+      <c r="D14" s="13">
+        <f>MONTH(B14)</f>
+        <v>8</v>
+      </c>
+      <c r="E14" s="15">
+        <f>DAY(B14)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B15" s="12">
-        <v>37929</v>
-      </c>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-    </row>
-    <row r="16" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+        <v>37703</v>
+      </c>
+      <c r="C15" s="15">
+        <f>YEAR(B15)</f>
+        <v>2003</v>
+      </c>
+      <c r="D15" s="13">
+        <f>MONTH(B15)</f>
+        <v>3</v>
+      </c>
+      <c r="E15" s="15">
+        <f>DAY(B15)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="B16" s="12">
-        <v>38189</v>
-      </c>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
+        <v>37644</v>
+      </c>
+      <c r="C16" s="15">
+        <f>YEAR(B16)</f>
+        <v>2003</v>
+      </c>
+      <c r="D16" s="13">
+        <f>MONTH(B16)</f>
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <f>DAY(B16)</f>
+        <v>23</v>
+      </c>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="12">
+        <v>37338</v>
+      </c>
+      <c r="C17" s="15">
+        <f>YEAR(B17)</f>
+        <v>2002</v>
+      </c>
+      <c r="D17" s="13">
+        <f>MONTH(B17)</f>
+        <v>3</v>
+      </c>
+      <c r="E17" s="15">
+        <f>DAY(B17)</f>
         <v>23</v>
       </c>
-      <c r="B17" s="12">
-        <v>37536</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
     </row>
     <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B18" s="12">
-        <v>38235</v>
-      </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
+        <v>38069</v>
+      </c>
+      <c r="C18" s="15">
+        <f>YEAR(B18)</f>
+        <v>2004</v>
+      </c>
+      <c r="D18" s="13">
+        <f>MONTH(B18)</f>
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <f>DAY(B18)</f>
+        <v>23</v>
+      </c>
     </row>
     <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B19" s="12">
-        <v>37757</v>
-      </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
+        <v>37794</v>
+      </c>
+      <c r="C19" s="15">
+        <f>YEAR(B19)</f>
+        <v>2003</v>
+      </c>
+      <c r="D19" s="13">
+        <f>MONTH(B19)</f>
+        <v>6</v>
+      </c>
+      <c r="E19" s="15">
+        <f>DAY(B19)</f>
+        <v>22</v>
+      </c>
     </row>
     <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B20" s="12">
-        <v>37957</v>
-      </c>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
+        <v>38160</v>
+      </c>
+      <c r="C20" s="15">
+        <f>YEAR(B20)</f>
+        <v>2004</v>
+      </c>
+      <c r="D20" s="13">
+        <f>MONTH(B20)</f>
+        <v>6</v>
+      </c>
+      <c r="E20" s="15">
+        <f>DAY(B20)</f>
+        <v>22</v>
+      </c>
     </row>
     <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B21" s="12">
-        <v>37794</v>
-      </c>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
+        <v>38189</v>
+      </c>
+      <c r="C21" s="15">
+        <f>YEAR(B21)</f>
+        <v>2004</v>
+      </c>
+      <c r="D21" s="13">
+        <f>MONTH(B21)</f>
+        <v>7</v>
+      </c>
+      <c r="E21" s="15">
+        <f>DAY(B21)</f>
+        <v>21</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="11" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B22" s="12">
-        <v>38160</v>
-      </c>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
+        <v>38312</v>
+      </c>
+      <c r="C22" s="15">
+        <f>YEAR(B22)</f>
+        <v>2004</v>
+      </c>
+      <c r="D22" s="13">
+        <f>MONTH(B22)</f>
+        <v>11</v>
+      </c>
+      <c r="E22" s="15">
+        <f>DAY(B22)</f>
+        <v>21</v>
+      </c>
     </row>
     <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="11" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B23" s="12">
-        <v>37865</v>
-      </c>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
+        <v>37547</v>
+      </c>
+      <c r="C23" s="15">
+        <f>YEAR(B23)</f>
+        <v>2002</v>
+      </c>
+      <c r="D23" s="13">
+        <f>MONTH(B23)</f>
+        <v>10</v>
+      </c>
+      <c r="E23" s="15">
+        <f>DAY(B23)</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="11" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B24" s="12">
-        <v>37703</v>
-      </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
+        <v>38460</v>
+      </c>
+      <c r="C24" s="15">
+        <f>YEAR(B24)</f>
+        <v>2005</v>
+      </c>
+      <c r="D24" s="13">
+        <f>MONTH(B24)</f>
+        <v>4</v>
+      </c>
+      <c r="E24" s="15">
+        <f>DAY(B24)</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="B25" s="12">
-        <v>38458</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
+        <v>38429</v>
+      </c>
+      <c r="C25" s="15">
+        <f>YEAR(B25)</f>
+        <v>2005</v>
+      </c>
+      <c r="D25" s="13">
+        <f>MONTH(B25)</f>
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <f>DAY(B25)</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="11" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="B26" s="12">
-        <v>38185</v>
-      </c>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
+        <v>38428</v>
+      </c>
+      <c r="C26" s="15">
+        <f>YEAR(B26)</f>
+        <v>2005</v>
+      </c>
+      <c r="D26" s="13">
+        <f>MONTH(B26)</f>
+        <v>3</v>
+      </c>
+      <c r="E26" s="15">
+        <f>DAY(B26)</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="12">
-        <v>38349</v>
-      </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
+        <v>38185</v>
+      </c>
+      <c r="C27" s="15">
+        <f>YEAR(B27)</f>
+        <v>2004</v>
+      </c>
+      <c r="D27" s="13">
+        <f>MONTH(B27)</f>
+        <v>7</v>
+      </c>
+      <c r="E27" s="15">
+        <f>DAY(B27)</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="11" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B28" s="12">
-        <v>37547</v>
-      </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
+        <v>37304</v>
+      </c>
+      <c r="C28" s="15">
+        <f>YEAR(B28)</f>
+        <v>2002</v>
+      </c>
+      <c r="D28" s="13">
+        <f>MONTH(B28)</f>
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <f>DAY(B28)</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B29" s="12">
-        <v>37298</v>
-      </c>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
+        <v>37757</v>
+      </c>
+      <c r="C29" s="15">
+        <f>YEAR(B29)</f>
+        <v>2003</v>
+      </c>
+      <c r="D29" s="13">
+        <f>MONTH(B29)</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="15">
+        <f>DAY(B29)</f>
+        <v>16</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="11" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B30" s="12">
-        <v>37970</v>
-      </c>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
+        <v>38458</v>
+      </c>
+      <c r="C30" s="15">
+        <f>YEAR(B30)</f>
+        <v>2005</v>
+      </c>
+      <c r="D30" s="13">
+        <f>MONTH(B30)</f>
+        <v>4</v>
+      </c>
+      <c r="E30" s="15">
+        <f>DAY(B30)</f>
+        <v>16</v>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="11" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B31" s="12">
-        <v>37390</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
+        <v>38275</v>
+      </c>
+      <c r="C31" s="15">
+        <f>YEAR(B31)</f>
+        <v>2004</v>
+      </c>
+      <c r="D31" s="13">
+        <f>MONTH(B31)</f>
+        <v>10</v>
+      </c>
+      <c r="E31" s="15">
+        <f>DAY(B31)</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B32" s="12">
-        <v>37806</v>
-      </c>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
+        <v>37970</v>
+      </c>
+      <c r="C32" s="15">
+        <f>YEAR(B32)</f>
+        <v>2003</v>
+      </c>
+      <c r="D32" s="13">
+        <f>MONTH(B32)</f>
+        <v>12</v>
+      </c>
+      <c r="E32" s="15">
+        <f>DAY(B32)</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B33" s="12">
-        <v>37601</v>
-      </c>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
+        <v>37390</v>
+      </c>
+      <c r="C33" s="15">
+        <f>YEAR(B33)</f>
+        <v>2002</v>
+      </c>
+      <c r="D33" s="13">
+        <f>MONTH(B33)</f>
+        <v>5</v>
+      </c>
+      <c r="E33" s="15">
+        <f>DAY(B33)</f>
+        <v>14</v>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="11" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B34" s="12">
-        <v>37283</v>
-      </c>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
+        <v>36721</v>
+      </c>
+      <c r="C34" s="15">
+        <f>YEAR(B34)</f>
+        <v>2000</v>
+      </c>
+      <c r="D34" s="13">
+        <f>MONTH(B34)</f>
+        <v>7</v>
+      </c>
+      <c r="E34" s="15">
+        <f>DAY(B34)</f>
+        <v>14</v>
+      </c>
     </row>
     <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="11" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B35" s="12">
-        <v>37644</v>
-      </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
+        <v>37665</v>
+      </c>
+      <c r="C35" s="15">
+        <f>YEAR(B35)</f>
+        <v>2003</v>
+      </c>
+      <c r="D35" s="13">
+        <f>MONTH(B35)</f>
+        <v>2</v>
+      </c>
+      <c r="E35" s="15">
+        <f>DAY(B35)</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="11" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B36" s="12">
-        <v>38312</v>
-      </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
+        <v>37997</v>
+      </c>
+      <c r="C36" s="15">
+        <f>YEAR(B36)</f>
+        <v>2004</v>
+      </c>
+      <c r="D36" s="13">
+        <f>MONTH(B36)</f>
+        <v>1</v>
+      </c>
+      <c r="E36" s="15">
+        <f>DAY(B36)</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="11" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B37" s="12">
-        <v>37473</v>
-      </c>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
+        <v>37298</v>
+      </c>
+      <c r="C37" s="15">
+        <f>YEAR(B37)</f>
+        <v>2002</v>
+      </c>
+      <c r="D37" s="13">
+        <f>MONTH(B37)</f>
+        <v>2</v>
+      </c>
+      <c r="E37" s="15">
+        <f>DAY(B37)</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="11" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B38" s="12">
-        <v>37338</v>
-      </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
+        <v>37601</v>
+      </c>
+      <c r="C38" s="15">
+        <f>YEAR(B38)</f>
+        <v>2002</v>
+      </c>
+      <c r="D38" s="13">
+        <f>MONTH(B38)</f>
+        <v>12</v>
+      </c>
+      <c r="E38" s="15">
+        <f>DAY(B38)</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B39" s="12">
-        <v>38069</v>
-      </c>
-      <c r="C39" s="10"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="10"/>
+        <v>38028</v>
+      </c>
+      <c r="C39" s="15">
+        <f>YEAR(B39)</f>
+        <v>2004</v>
+      </c>
+      <c r="D39" s="13">
+        <f>MONTH(B39)</f>
+        <v>2</v>
+      </c>
+      <c r="E39" s="15">
+        <f>DAY(B39)</f>
+        <v>11</v>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="11" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B40" s="12">
-        <v>38290</v>
-      </c>
-      <c r="C40" s="10"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="10"/>
+        <v>37965</v>
+      </c>
+      <c r="C40" s="15">
+        <f>YEAR(B40)</f>
+        <v>2003</v>
+      </c>
+      <c r="D40" s="13">
+        <f>MONTH(B40)</f>
+        <v>12</v>
+      </c>
+      <c r="E40" s="15">
+        <f>DAY(B40)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="B41" s="12">
-        <v>37304</v>
-      </c>
-      <c r="C41" s="10"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="10"/>
+        <v>37536</v>
+      </c>
+      <c r="C41" s="15">
+        <f>YEAR(B41)</f>
+        <v>2002</v>
+      </c>
+      <c r="D41" s="13">
+        <f>MONTH(B41)</f>
+        <v>10</v>
+      </c>
+      <c r="E41" s="15">
+        <f>DAY(B41)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="11" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B42" s="12">
-        <v>36721</v>
-      </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
+        <v>37748</v>
+      </c>
+      <c r="C42" s="15">
+        <f>YEAR(B42)</f>
+        <v>2003</v>
+      </c>
+      <c r="D42" s="13">
+        <f>MONTH(B42)</f>
+        <v>5</v>
+      </c>
+      <c r="E42" s="15">
+        <f>DAY(B42)</f>
+        <v>7</v>
+      </c>
     </row>
     <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="12">
-        <v>37925</v>
-      </c>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
+        <v>38023</v>
+      </c>
+      <c r="C43" s="15">
+        <f>YEAR(B43)</f>
+        <v>2004</v>
+      </c>
+      <c r="D43" s="13">
+        <f>MONTH(B43)</f>
+        <v>2</v>
+      </c>
+      <c r="E43" s="15">
+        <f>DAY(B43)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="11" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B44" s="12">
-        <v>37665</v>
-      </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
+        <v>38296</v>
+      </c>
+      <c r="C44" s="15">
+        <f>YEAR(B44)</f>
+        <v>2004</v>
+      </c>
+      <c r="D44" s="13">
+        <f>MONTH(B44)</f>
+        <v>11</v>
+      </c>
+      <c r="E44" s="15">
+        <f>DAY(B44)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="11" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B45" s="12">
-        <v>38023</v>
-      </c>
-      <c r="C45" s="10"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="10"/>
+        <v>37442</v>
+      </c>
+      <c r="C45" s="15">
+        <f>YEAR(B45)</f>
+        <v>2002</v>
+      </c>
+      <c r="D45" s="13">
+        <f>MONTH(B45)</f>
+        <v>7</v>
+      </c>
+      <c r="E45" s="15">
+        <f>DAY(B45)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="46" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="11" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B46" s="12">
-        <v>38028</v>
-      </c>
-      <c r="C46" s="10"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="10"/>
+        <v>38235</v>
+      </c>
+      <c r="C46" s="15">
+        <f>YEAR(B46)</f>
+        <v>2004</v>
+      </c>
+      <c r="D46" s="13">
+        <f>MONTH(B46)</f>
+        <v>9</v>
+      </c>
+      <c r="E46" s="15">
+        <f>DAY(B46)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B47" s="12">
-        <v>38460</v>
-      </c>
-      <c r="C47" s="10"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="10"/>
+        <v>37473</v>
+      </c>
+      <c r="C47" s="15">
+        <f>YEAR(B47)</f>
+        <v>2002</v>
+      </c>
+      <c r="D47" s="13">
+        <f>MONTH(B47)</f>
+        <v>8</v>
+      </c>
+      <c r="E47" s="15">
+        <f>DAY(B47)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="48" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="11" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="B48" s="12">
-        <v>37866</v>
-      </c>
-      <c r="C48" s="10"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="10"/>
+        <v>37929</v>
+      </c>
+      <c r="C48" s="15">
+        <f>YEAR(B48)</f>
+        <v>2003</v>
+      </c>
+      <c r="D48" s="13">
+        <f>MONTH(B48)</f>
+        <v>11</v>
+      </c>
+      <c r="E48" s="15">
+        <f>DAY(B48)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="49" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="11" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B49" s="12">
-        <v>37195</v>
-      </c>
-      <c r="C49" s="10"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="10"/>
+        <v>37806</v>
+      </c>
+      <c r="C49" s="15">
+        <f>YEAR(B49)</f>
+        <v>2003</v>
+      </c>
+      <c r="D49" s="13">
+        <f>MONTH(B49)</f>
+        <v>7</v>
+      </c>
+      <c r="E49" s="15">
+        <f>DAY(B49)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="50" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="12">
-        <v>37893</v>
-      </c>
-      <c r="C50" s="10"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="10"/>
+        <v>37503</v>
+      </c>
+      <c r="C50" s="15">
+        <f>YEAR(B50)</f>
+        <v>2002</v>
+      </c>
+      <c r="D50" s="13">
+        <f>MONTH(B50)</f>
+        <v>9</v>
+      </c>
+      <c r="E50" s="15">
+        <f>DAY(B50)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="51" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="11" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="B51" s="12">
-        <v>37503</v>
-      </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
+        <v>37714</v>
+      </c>
+      <c r="C51" s="15">
+        <f>YEAR(B51)</f>
+        <v>2003</v>
+      </c>
+      <c r="D51" s="13">
+        <f>MONTH(B51)</f>
+        <v>4</v>
+      </c>
+      <c r="E51" s="15">
+        <f>DAY(B51)</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="52" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="B52" s="12">
-        <v>38351</v>
-      </c>
-      <c r="C52" s="10"/>
-      <c r="D52" s="10"/>
-      <c r="E52" s="10"/>
+        <v>37957</v>
+      </c>
+      <c r="C52" s="15">
+        <f>YEAR(B52)</f>
+        <v>2003</v>
+      </c>
+      <c r="D52" s="13">
+        <f>MONTH(B52)</f>
+        <v>12</v>
+      </c>
+      <c r="E52" s="15">
+        <f>DAY(B52)</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="53" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B53" s="12">
-        <v>38429</v>
-      </c>
-      <c r="C53" s="10"/>
-      <c r="D53" s="10"/>
-      <c r="E53" s="10"/>
-    </row>
-    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="8"/>
-      <c r="B54" s="8"/>
+        <v>37866</v>
+      </c>
+      <c r="C53" s="15">
+        <f>YEAR(B53)</f>
+        <v>2003</v>
+      </c>
+      <c r="D53" s="13">
+        <f>MONTH(B53)</f>
+        <v>9</v>
+      </c>
+      <c r="E53" s="15">
+        <f>DAY(B53)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="12">
+        <v>37865</v>
+      </c>
+      <c r="C54" s="15">
+        <f>YEAR(B54)</f>
+        <v>2003</v>
+      </c>
+      <c r="D54" s="13">
+        <f>MONTH(B54)</f>
+        <v>9</v>
+      </c>
+      <c r="E54" s="15">
+        <f>DAY(B54)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="7"/>
-      <c r="B55" s="7"/>
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
     </row>
     <row r="56" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="7"/>
@@ -4671,6 +5341,1635 @@
     <row r="884" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A884" s="7"/>
       <c r="B884" s="7"/>
+    </row>
+    <row r="885" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A885" s="7"/>
+      <c r="B885" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD89DCB-594D-4077-8D8E-17BC227A74D9}">
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="18">
+        <v>45717</v>
+      </c>
+      <c r="C2" s="20">
+        <v>7</v>
+      </c>
+      <c r="D2" s="21">
+        <f>B2+C2</f>
+        <v>45724</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="18">
+        <v>45719</v>
+      </c>
+      <c r="C3" s="20">
+        <v>8</v>
+      </c>
+      <c r="D3" s="21">
+        <f t="shared" ref="D3:D11" si="0">B3+C3</f>
+        <v>45727</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" s="18">
+        <v>45721</v>
+      </c>
+      <c r="C4" s="20">
+        <v>6</v>
+      </c>
+      <c r="D4" s="21">
+        <f t="shared" si="0"/>
+        <v>45727</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B5" s="18">
+        <v>45723</v>
+      </c>
+      <c r="C5" s="20">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>45725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B6" s="18">
+        <v>45726</v>
+      </c>
+      <c r="C6" s="20">
+        <v>8</v>
+      </c>
+      <c r="D6" s="21">
+        <f t="shared" si="0"/>
+        <v>45734</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B7" s="18">
+        <v>45728</v>
+      </c>
+      <c r="C7" s="20">
+        <v>4</v>
+      </c>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>45732</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="18">
+        <v>45731</v>
+      </c>
+      <c r="C8" s="20">
+        <v>4</v>
+      </c>
+      <c r="D8" s="21">
+        <f t="shared" si="0"/>
+        <v>45735</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="18">
+        <v>45734</v>
+      </c>
+      <c r="C9" s="20">
+        <v>5</v>
+      </c>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>45739</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="18">
+        <v>45736</v>
+      </c>
+      <c r="C10" s="20">
+        <v>6</v>
+      </c>
+      <c r="D10" s="21">
+        <f t="shared" si="0"/>
+        <v>45742</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="18">
+        <v>45741</v>
+      </c>
+      <c r="C11" s="20">
+        <v>9</v>
+      </c>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>45750</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="18">
+        <v>45717</v>
+      </c>
+      <c r="C18" s="20">
+        <v>7</v>
+      </c>
+      <c r="D18" s="23">
+        <f>EDATE(B18,C18)</f>
+        <v>45931</v>
+      </c>
+      <c r="E18" s="22"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="18">
+        <v>45719</v>
+      </c>
+      <c r="C19" s="20">
+        <v>8</v>
+      </c>
+      <c r="D19" s="23">
+        <f t="shared" ref="D19:D27" si="1">EDATE(B19,C19)</f>
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B20" s="18">
+        <v>45721</v>
+      </c>
+      <c r="C20" s="20">
+        <v>6</v>
+      </c>
+      <c r="D20" s="23">
+        <f t="shared" si="1"/>
+        <v>45905</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="18">
+        <v>45723</v>
+      </c>
+      <c r="C21" s="20">
+        <v>2</v>
+      </c>
+      <c r="D21" s="23">
+        <f t="shared" si="1"/>
+        <v>45784</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="18">
+        <v>45726</v>
+      </c>
+      <c r="C22" s="20">
+        <v>8</v>
+      </c>
+      <c r="D22" s="23">
+        <f t="shared" si="1"/>
+        <v>45971</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" s="18">
+        <v>45728</v>
+      </c>
+      <c r="C23" s="20">
+        <v>4</v>
+      </c>
+      <c r="D23" s="23">
+        <f t="shared" si="1"/>
+        <v>45850</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B24" s="18">
+        <v>45731</v>
+      </c>
+      <c r="C24" s="20">
+        <v>4</v>
+      </c>
+      <c r="D24" s="23">
+        <f t="shared" si="1"/>
+        <v>45853</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B25" s="18">
+        <v>45734</v>
+      </c>
+      <c r="C25" s="20">
+        <v>5</v>
+      </c>
+      <c r="D25" s="23">
+        <f t="shared" si="1"/>
+        <v>45887</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="18">
+        <v>45736</v>
+      </c>
+      <c r="C26" s="20">
+        <v>6</v>
+      </c>
+      <c r="D26" s="23">
+        <f t="shared" si="1"/>
+        <v>45920</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B27" s="18">
+        <v>45741</v>
+      </c>
+      <c r="C27" s="20">
+        <v>9</v>
+      </c>
+      <c r="D27" s="23">
+        <f t="shared" si="1"/>
+        <v>46016</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A33" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="18">
+        <v>45717</v>
+      </c>
+      <c r="C33" s="20">
+        <v>7</v>
+      </c>
+      <c r="D33" s="18">
+        <f>EDATE(B33,C33*12)</f>
+        <v>48274</v>
+      </c>
+      <c r="E33" s="18">
+        <v>48274</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A34" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="18">
+        <v>45719</v>
+      </c>
+      <c r="C34" s="20">
+        <v>8</v>
+      </c>
+      <c r="D34" s="18">
+        <f t="shared" ref="D34:D42" si="2">EDATE(B34,C34*12)</f>
+        <v>48641</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A35" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="18">
+        <v>45721</v>
+      </c>
+      <c r="C35" s="20">
+        <v>6</v>
+      </c>
+      <c r="D35" s="18">
+        <f t="shared" si="2"/>
+        <v>47912</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A36" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="18">
+        <v>45723</v>
+      </c>
+      <c r="C36" s="20">
+        <v>2</v>
+      </c>
+      <c r="D36" s="18">
+        <f t="shared" si="2"/>
+        <v>46453</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A37" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B37" s="18">
+        <v>45726</v>
+      </c>
+      <c r="C37" s="20">
+        <v>8</v>
+      </c>
+      <c r="D37" s="18">
+        <f t="shared" si="2"/>
+        <v>48648</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A38" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="18">
+        <v>45728</v>
+      </c>
+      <c r="C38" s="20">
+        <v>4</v>
+      </c>
+      <c r="D38" s="18">
+        <f t="shared" si="2"/>
+        <v>47189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A39" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="18">
+        <v>45731</v>
+      </c>
+      <c r="C39" s="20">
+        <v>4</v>
+      </c>
+      <c r="D39" s="18">
+        <f t="shared" si="2"/>
+        <v>47192</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A40" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="18">
+        <v>45734</v>
+      </c>
+      <c r="C40" s="20">
+        <v>5</v>
+      </c>
+      <c r="D40" s="18">
+        <f t="shared" si="2"/>
+        <v>47560</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A41" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="18">
+        <v>45736</v>
+      </c>
+      <c r="C41" s="20">
+        <v>6</v>
+      </c>
+      <c r="D41" s="18">
+        <f t="shared" si="2"/>
+        <v>47927</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A42" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="18">
+        <v>45741</v>
+      </c>
+      <c r="C42" s="20">
+        <v>9</v>
+      </c>
+      <c r="D42" s="18">
+        <f t="shared" si="2"/>
+        <v>49028</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45E4F26-4BD6-46E1-942B-B0DD3B0185C8}">
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="12">
+        <v>37925</v>
+      </c>
+      <c r="C2" s="15">
+        <f ca="1">DATEDIF(B2,TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D2" s="15">
+        <f ca="1">DATEDIF(B2,TODAY(),"m")</f>
+        <v>274</v>
+      </c>
+      <c r="E2" s="10">
+        <f ca="1">DATEDIF(B2,TODAY(),"D")</f>
+        <v>8369</v>
+      </c>
+      <c r="H2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="12">
+        <v>37195</v>
+      </c>
+      <c r="C3" s="15">
+        <f t="shared" ref="C3:C54" ca="1" si="0">DATEDIF(B3,TODAY(),"Y")</f>
+        <v>24</v>
+      </c>
+      <c r="D3" s="15">
+        <f t="shared" ref="D3:D54" ca="1" si="1">DATEDIF(B3,TODAY(),"m")</f>
+        <v>298</v>
+      </c>
+      <c r="E3" s="10">
+        <f t="shared" ref="E3:E54" ca="1" si="2">DATEDIF(B3,TODAY(),"D")</f>
+        <v>9099</v>
+      </c>
+      <c r="H3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="12">
+        <v>37832</v>
+      </c>
+      <c r="C4" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D4" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>277</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8462</v>
+      </c>
+      <c r="H4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="12">
+        <v>37710</v>
+      </c>
+      <c r="C5" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D5" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>281</v>
+      </c>
+      <c r="E5" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8584</v>
+      </c>
+      <c r="H5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="12">
+        <v>38290</v>
+      </c>
+      <c r="C6" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D6" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>262</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8004</v>
+      </c>
+      <c r="H6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="12">
+        <v>38351</v>
+      </c>
+      <c r="C7" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D7" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>260</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7943</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="12">
+        <v>37893</v>
+      </c>
+      <c r="C8" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D8" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>276</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8401</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="12">
+        <v>38349</v>
+      </c>
+      <c r="C9" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D9" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>261</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7945</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="12">
+        <v>37283</v>
+      </c>
+      <c r="C10" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D10" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>296</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>9011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="12">
+        <v>38408</v>
+      </c>
+      <c r="C11" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D11" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>259</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7886</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12">
+        <v>37704</v>
+      </c>
+      <c r="C12" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D12" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>282</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8590</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="12">
+        <v>37826</v>
+      </c>
+      <c r="C13" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D13" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>278</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8468</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" s="12">
+        <v>37126</v>
+      </c>
+      <c r="C14" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="D14" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>301</v>
+      </c>
+      <c r="E14" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>9168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="12">
+        <v>37703</v>
+      </c>
+      <c r="C15" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D15" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>282</v>
+      </c>
+      <c r="E15" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8591</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="12">
+        <v>37644</v>
+      </c>
+      <c r="C16" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D16" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>284</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8650</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="12">
+        <v>37338</v>
+      </c>
+      <c r="C17" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D17" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>294</v>
+      </c>
+      <c r="E17" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8956</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="12">
+        <v>38069</v>
+      </c>
+      <c r="C18" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D18" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="E18" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8225</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="12">
+        <v>37794</v>
+      </c>
+      <c r="C19" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D19" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>279</v>
+      </c>
+      <c r="E19" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="12">
+        <v>38160</v>
+      </c>
+      <c r="C20" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D20" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>267</v>
+      </c>
+      <c r="E20" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="12">
+        <v>38189</v>
+      </c>
+      <c r="C21" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D21" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>266</v>
+      </c>
+      <c r="E21" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="12">
+        <v>38312</v>
+      </c>
+      <c r="C22" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D22" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>262</v>
+      </c>
+      <c r="E22" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7982</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="12">
+        <v>37547</v>
+      </c>
+      <c r="C23" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D23" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>287</v>
+      </c>
+      <c r="E23" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8747</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="12">
+        <v>38460</v>
+      </c>
+      <c r="C24" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D24" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>257</v>
+      </c>
+      <c r="E24" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7834</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="12">
+        <v>38429</v>
+      </c>
+      <c r="C25" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D25" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>258</v>
+      </c>
+      <c r="E25" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7865</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="12">
+        <v>38428</v>
+      </c>
+      <c r="C26" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D26" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>258</v>
+      </c>
+      <c r="E26" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7866</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="12">
+        <v>38185</v>
+      </c>
+      <c r="C27" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D27" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>266</v>
+      </c>
+      <c r="E27" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="12">
+        <v>37304</v>
+      </c>
+      <c r="C28" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D28" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>295</v>
+      </c>
+      <c r="E28" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8990</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="12">
+        <v>37757</v>
+      </c>
+      <c r="C29" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D29" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>280</v>
+      </c>
+      <c r="E29" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8537</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="12">
+        <v>38458</v>
+      </c>
+      <c r="C30" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D30" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>257</v>
+      </c>
+      <c r="E30" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7836</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="12">
+        <v>38275</v>
+      </c>
+      <c r="C31" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D31" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>263</v>
+      </c>
+      <c r="E31" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8019</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="12">
+        <v>37970</v>
+      </c>
+      <c r="C32" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D32" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>273</v>
+      </c>
+      <c r="E32" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8324</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="12">
+        <v>37390</v>
+      </c>
+      <c r="C33" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D33" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>292</v>
+      </c>
+      <c r="E33" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8904</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="12">
+        <v>36721</v>
+      </c>
+      <c r="C34" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D34" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>314</v>
+      </c>
+      <c r="E34" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>9573</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="12">
+        <v>37665</v>
+      </c>
+      <c r="C35" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D35" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>283</v>
+      </c>
+      <c r="E35" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8629</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="12">
+        <v>37997</v>
+      </c>
+      <c r="C36" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D36" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>272</v>
+      </c>
+      <c r="E36" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8297</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="12">
+        <v>37298</v>
+      </c>
+      <c r="C37" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D37" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>295</v>
+      </c>
+      <c r="E37" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8996</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="12">
+        <v>37601</v>
+      </c>
+      <c r="C38" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D38" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>285</v>
+      </c>
+      <c r="E38" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8693</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="12">
+        <v>38028</v>
+      </c>
+      <c r="C39" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D39" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>271</v>
+      </c>
+      <c r="E39" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8266</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="12">
+        <v>37965</v>
+      </c>
+      <c r="C40" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D40" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>273</v>
+      </c>
+      <c r="E40" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8329</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="12">
+        <v>37536</v>
+      </c>
+      <c r="C41" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D41" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>287</v>
+      </c>
+      <c r="E41" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8758</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="12">
+        <v>37748</v>
+      </c>
+      <c r="C42" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D42" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>280</v>
+      </c>
+      <c r="E42" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8546</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="12">
+        <v>38023</v>
+      </c>
+      <c r="C43" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D43" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>271</v>
+      </c>
+      <c r="E43" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8271</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="12">
+        <v>38296</v>
+      </c>
+      <c r="C44" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D44" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>262</v>
+      </c>
+      <c r="E44" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>7998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="12">
+        <v>37442</v>
+      </c>
+      <c r="C45" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D45" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>290</v>
+      </c>
+      <c r="E45" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8852</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="12">
+        <v>38235</v>
+      </c>
+      <c r="C46" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D46" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>264</v>
+      </c>
+      <c r="E46" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8059</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="12">
+        <v>37473</v>
+      </c>
+      <c r="C47" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D47" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>289</v>
+      </c>
+      <c r="E47" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8821</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="12">
+        <v>37929</v>
+      </c>
+      <c r="C48" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D48" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>274</v>
+      </c>
+      <c r="E48" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8365</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="12">
+        <v>37806</v>
+      </c>
+      <c r="C49" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D49" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>278</v>
+      </c>
+      <c r="E49" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8488</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="12">
+        <v>37503</v>
+      </c>
+      <c r="C50" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D50" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>288</v>
+      </c>
+      <c r="E50" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8791</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="12">
+        <v>37714</v>
+      </c>
+      <c r="C51" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D51" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>281</v>
+      </c>
+      <c r="E51" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8580</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="12">
+        <v>37957</v>
+      </c>
+      <c r="C52" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D52" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>273</v>
+      </c>
+      <c r="E52" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8337</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="12">
+        <v>37866</v>
+      </c>
+      <c r="C53" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D53" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>276</v>
+      </c>
+      <c r="E53" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8428</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="12">
+        <v>37865</v>
+      </c>
+      <c r="C54" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D54" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>276</v>
+      </c>
+      <c r="E54" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>8429</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/DateFunctions8001.xlsx
+++ b/Excel/DateFunctions8001.xlsx
@@ -8,16 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA22EFCF-0C0A-4B27-BA89-F009E9291851}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90554C8-A9AF-4F84-A5FB-94BB6C0AC491}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="4" xr2:uid="{FFAF0F3A-FACC-44CD-90E3-6CA7DF844403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="7" xr2:uid="{FFAF0F3A-FACC-44CD-90E3-6CA7DF844403}"/>
   </bookViews>
   <sheets>
     <sheet name="Today" sheetId="1" r:id="rId1"/>
     <sheet name="Now" sheetId="2" r:id="rId2"/>
     <sheet name="YearMonthDay" sheetId="3" r:id="rId3"/>
     <sheet name="EDate" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet4" sheetId="6" r:id="rId5"/>
+    <sheet name="Datedif" sheetId="6" r:id="rId5"/>
+    <sheet name="Chart2" sheetId="9" r:id="rId6"/>
+    <sheet name="Chart1" sheetId="8" r:id="rId7"/>
+    <sheet name="AgeCalculation" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">YearMonthDay!$A$1:$E$54</definedName>
@@ -32,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="93">
   <si>
     <t>EmployeeNam</t>
   </si>
@@ -309,6 +312,9 @@
   <si>
     <t>24 years 2 month 1 day old</t>
   </si>
+  <si>
+    <t>FinalResult</t>
+  </si>
 </sst>
 </file>
 
@@ -316,7 +322,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00000"/>
-    <numFmt numFmtId="169" formatCode="[$-409]d/mmm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]d/mmm/yy;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -360,7 +366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -383,6 +389,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF002060"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -450,7 +462,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -485,7 +497,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -494,11 +506,28 @@
     <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -516,6 +545,1998 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>AgeCalculation!$F$2:$F$53</c:f>
+              <c:strCache>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>25 Years 1 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22 Years 11 months 0 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24 Years 11 months 0 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23 Years 2 months 1 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23 Years 6 months 1 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21 Years 11 months 1 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21 Years 9 months 1 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23 Years 0 months 2 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21 Years 9 months 3 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24 Years 8 months 4 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21 Years 7 months 6 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>23 Years 6 months 7 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>23 Years 2 months 7 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23 Years 6 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23 Years 8 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>24 Years 6 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>22 Years 6 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23 Years 3 months 9 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22 Years 3 months 9 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>22 Years 2 months 10 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21 Years 10 months 10 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23 Years 11 months 13 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>21 Years 5 months 13 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>21 Years 6 months 13 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21 Years 6 months 14 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>22 Years 2 months 14 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>24 Years 7 months 14 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>23 Years 4 months 15 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>21 Years 5 months 15 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>21 Years 11 months 16 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>22 Years 9 months 16 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>24 Years 4 months 17 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26 Years 2 months 17 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>23 Years 7 months 18 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>22 Years 8 months 20 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>24 Years 7 months 20 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>23 Years 9 months 20 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>22 Years 7 months 20 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>22 Years 9 months 21 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>23 Years 11 months 24 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>23 Years 4 months 24 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>22 Years 7 months 25 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>21 Years 10 months 26 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>24 Years 2 months 26 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>22 Years 0 months 26 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>24 Years 1 months 26 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>22 Years 10 months 27 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>23 Years 2 months 27 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>24 Years 0 months 27 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>23 Years 5 months 28 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>22 Years 9 months 29 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>23 Years 0 months 29 Days Old</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>AgeCalculation!$F$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3A08-433E-ACB5-61F1DBEEF93D}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1307867151"/>
+        <c:axId val="1305799583"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1307867151"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1305799583"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1305799583"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1307867151"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>AgeCalculation!$F$2:$F$53</c:f>
+              <c:strCache>
+                <c:ptCount val="52"/>
+                <c:pt idx="0">
+                  <c:v>25 Years 1 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22 Years 11 months 0 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24 Years 11 months 0 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>23 Years 2 months 1 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23 Years 6 months 1 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>21 Years 11 months 1 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21 Years 9 months 1 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>23 Years 0 months 2 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>21 Years 9 months 3 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>24 Years 8 months 4 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>21 Years 7 months 6 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>23 Years 6 months 7 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>23 Years 2 months 7 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>23 Years 6 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>23 Years 8 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>24 Years 6 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>22 Years 6 months 8 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>23 Years 3 months 9 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>22 Years 3 months 9 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>22 Years 2 months 10 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21 Years 10 months 10 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>23 Years 11 months 13 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>21 Years 5 months 13 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>21 Years 6 months 13 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>21 Years 6 months 14 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>22 Years 2 months 14 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>24 Years 7 months 14 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>23 Years 4 months 15 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>21 Years 5 months 15 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>21 Years 11 months 16 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>22 Years 9 months 16 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>24 Years 4 months 17 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>26 Years 2 months 17 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>23 Years 7 months 18 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>22 Years 8 months 20 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>24 Years 7 months 20 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>23 Years 9 months 20 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>22 Years 7 months 20 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>22 Years 9 months 21 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>23 Years 11 months 24 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>23 Years 4 months 24 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>22 Years 7 months 25 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>21 Years 10 months 26 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>24 Years 2 months 26 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>22 Years 0 months 26 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>24 Years 1 months 26 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>22 Years 10 months 27 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>23 Years 2 months 27 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>24 Years 0 months 27 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>23 Years 5 months 28 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>22 Years 9 months 29 Days Old</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>23 Years 0 months 29 Days Old</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>AgeCalculation!$F$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-4703-4ADA-820A-2113323E15C0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1309005071"/>
+        <c:axId val="1242681007"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1309005071"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1242681007"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1242681007"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1309005071"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{881F2ED7-09EC-46A8-A460-945179BE85D1}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/chartsheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{CF75D916-A187-4369-88C9-4434133A842D}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8664677" cy="6288548"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C78A819-ED8E-445B-ABAF-0164C3C5CF3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8664677" cy="6288548"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C67FCAD-2F6B-4977-B5B3-52CBB14D199A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks noGrp="1"/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -875,15 +2896,15 @@
       </c>
       <c r="C3" s="3">
         <f ca="1">TODAY()</f>
-        <v>46294</v>
+        <v>46296</v>
       </c>
       <c r="D3" s="2">
         <f ca="1">C3-B3</f>
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E3" s="4">
         <f ca="1">D3/365</f>
-        <v>1.2438356164383562</v>
+        <v>1.2493150684931507</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">ROUNDUP(E3,2)</f>
@@ -914,7 +2935,7 @@
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="6">
         <f ca="1">NOW()</f>
-        <v>46294.532499652778</v>
+        <v>46296.474531250002</v>
       </c>
     </row>
   </sheetData>
@@ -961,15 +2982,15 @@
         <v>37925</v>
       </c>
       <c r="C2" s="15">
-        <f>YEAR(B2)</f>
+        <f t="shared" ref="C2:C33" si="0">YEAR(B2)</f>
         <v>2003</v>
       </c>
       <c r="D2" s="13">
-        <f>MONTH(B2)</f>
+        <f t="shared" ref="D2:D33" si="1">MONTH(B2)</f>
         <v>10</v>
       </c>
       <c r="E2" s="15">
-        <f>DAY(B2)</f>
+        <f t="shared" ref="E2:E33" si="2">DAY(B2)</f>
         <v>31</v>
       </c>
       <c r="G2" t="s">
@@ -984,15 +3005,15 @@
         <v>37195</v>
       </c>
       <c r="C3" s="15">
-        <f>YEAR(B3)</f>
+        <f t="shared" si="0"/>
         <v>2001</v>
       </c>
       <c r="D3" s="13">
-        <f>MONTH(B3)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="E3" s="15">
-        <f>DAY(B3)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="G3" t="s">
@@ -1007,15 +3028,15 @@
         <v>37832</v>
       </c>
       <c r="C4" s="15">
-        <f>YEAR(B4)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D4" s="13">
-        <f>MONTH(B4)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="E4" s="15">
-        <f>DAY(B4)</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="G4" t="s">
@@ -1030,15 +3051,15 @@
         <v>37710</v>
       </c>
       <c r="C5" s="15">
-        <f>YEAR(B5)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D5" s="13">
-        <f>MONTH(B5)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E5" s="15">
-        <f>DAY(B5)</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
     </row>
@@ -1050,15 +3071,15 @@
         <v>38290</v>
       </c>
       <c r="C6" s="15">
-        <f>YEAR(B6)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D6" s="13">
-        <f>MONTH(B6)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="E6" s="15">
-        <f>DAY(B6)</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
     </row>
@@ -1070,15 +3091,15 @@
         <v>38351</v>
       </c>
       <c r="C7" s="15">
-        <f>YEAR(B7)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D7" s="13">
-        <f>MONTH(B7)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E7" s="15">
-        <f>DAY(B7)</f>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
     </row>
@@ -1090,15 +3111,15 @@
         <v>37893</v>
       </c>
       <c r="C8" s="15">
-        <f>YEAR(B8)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D8" s="13">
-        <f>MONTH(B8)</f>
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="E8" s="15">
-        <f>DAY(B8)</f>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
     </row>
@@ -1110,15 +3131,15 @@
         <v>38349</v>
       </c>
       <c r="C9" s="15">
-        <f>YEAR(B9)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D9" s="13">
-        <f>MONTH(B9)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E9" s="15">
-        <f>DAY(B9)</f>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
     </row>
@@ -1130,15 +3151,15 @@
         <v>37283</v>
       </c>
       <c r="C10" s="15">
-        <f>YEAR(B10)</f>
+        <f t="shared" si="0"/>
         <v>2002</v>
       </c>
       <c r="D10" s="13">
-        <f>MONTH(B10)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E10" s="15">
-        <f>DAY(B10)</f>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
     </row>
@@ -1150,15 +3171,15 @@
         <v>38408</v>
       </c>
       <c r="C11" s="15">
-        <f>YEAR(B11)</f>
+        <f t="shared" si="0"/>
         <v>2005</v>
       </c>
       <c r="D11" s="13">
-        <f>MONTH(B11)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E11" s="15">
-        <f>DAY(B11)</f>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
     </row>
@@ -1170,15 +3191,15 @@
         <v>37704</v>
       </c>
       <c r="C12" s="15">
-        <f>YEAR(B12)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D12" s="13">
-        <f>MONTH(B12)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E12" s="15">
-        <f>DAY(B12)</f>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
     </row>
@@ -1190,15 +3211,15 @@
         <v>37826</v>
       </c>
       <c r="C13" s="15">
-        <f>YEAR(B13)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D13" s="13">
-        <f>MONTH(B13)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="E13" s="15">
-        <f>DAY(B13)</f>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
     </row>
@@ -1210,15 +3231,15 @@
         <v>37126</v>
       </c>
       <c r="C14" s="15">
-        <f>YEAR(B14)</f>
+        <f t="shared" si="0"/>
         <v>2001</v>
       </c>
       <c r="D14" s="13">
-        <f>MONTH(B14)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="E14" s="15">
-        <f>DAY(B14)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
@@ -1230,15 +3251,15 @@
         <v>37703</v>
       </c>
       <c r="C15" s="15">
-        <f>YEAR(B15)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D15" s="13">
-        <f>MONTH(B15)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E15" s="15">
-        <f>DAY(B15)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
@@ -1250,15 +3271,15 @@
         <v>37644</v>
       </c>
       <c r="C16" s="15">
-        <f>YEAR(B16)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D16" s="13">
-        <f>MONTH(B16)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <f>DAY(B16)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
@@ -1270,15 +3291,15 @@
         <v>37338</v>
       </c>
       <c r="C17" s="15">
-        <f>YEAR(B17)</f>
+        <f t="shared" si="0"/>
         <v>2002</v>
       </c>
       <c r="D17" s="13">
-        <f>MONTH(B17)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E17" s="15">
-        <f>DAY(B17)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
@@ -1290,15 +3311,15 @@
         <v>38069</v>
       </c>
       <c r="C18" s="15">
-        <f>YEAR(B18)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D18" s="13">
-        <f>MONTH(B18)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <f>DAY(B18)</f>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
     </row>
@@ -1310,15 +3331,15 @@
         <v>37794</v>
       </c>
       <c r="C19" s="15">
-        <f>YEAR(B19)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D19" s="13">
-        <f>MONTH(B19)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <f>DAY(B19)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
     </row>
@@ -1330,15 +3351,15 @@
         <v>38160</v>
       </c>
       <c r="C20" s="15">
-        <f>YEAR(B20)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D20" s="13">
-        <f>MONTH(B20)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="E20" s="15">
-        <f>DAY(B20)</f>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
     </row>
@@ -1350,15 +3371,15 @@
         <v>38189</v>
       </c>
       <c r="C21" s="15">
-        <f>YEAR(B21)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D21" s="13">
-        <f>MONTH(B21)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="E21" s="15">
-        <f>DAY(B21)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
     </row>
@@ -1370,15 +3391,15 @@
         <v>38312</v>
       </c>
       <c r="C22" s="15">
-        <f>YEAR(B22)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D22" s="13">
-        <f>MONTH(B22)</f>
+        <f t="shared" si="1"/>
         <v>11</v>
       </c>
       <c r="E22" s="15">
-        <f>DAY(B22)</f>
+        <f t="shared" si="2"/>
         <v>21</v>
       </c>
     </row>
@@ -1390,15 +3411,15 @@
         <v>37547</v>
       </c>
       <c r="C23" s="15">
-        <f>YEAR(B23)</f>
+        <f t="shared" si="0"/>
         <v>2002</v>
       </c>
       <c r="D23" s="13">
-        <f>MONTH(B23)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="E23" s="15">
-        <f>DAY(B23)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
     </row>
@@ -1410,15 +3431,15 @@
         <v>38460</v>
       </c>
       <c r="C24" s="15">
-        <f>YEAR(B24)</f>
+        <f t="shared" si="0"/>
         <v>2005</v>
       </c>
       <c r="D24" s="13">
-        <f>MONTH(B24)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="E24" s="15">
-        <f>DAY(B24)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
     </row>
@@ -1430,15 +3451,15 @@
         <v>38429</v>
       </c>
       <c r="C25" s="15">
-        <f>YEAR(B25)</f>
+        <f t="shared" si="0"/>
         <v>2005</v>
       </c>
       <c r="D25" s="13">
-        <f>MONTH(B25)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E25" s="15">
-        <f>DAY(B25)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
     </row>
@@ -1450,15 +3471,15 @@
         <v>38428</v>
       </c>
       <c r="C26" s="15">
-        <f>YEAR(B26)</f>
+        <f t="shared" si="0"/>
         <v>2005</v>
       </c>
       <c r="D26" s="13">
-        <f>MONTH(B26)</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E26" s="15">
-        <f>DAY(B26)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
@@ -1470,15 +3491,15 @@
         <v>38185</v>
       </c>
       <c r="C27" s="15">
-        <f>YEAR(B27)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D27" s="13">
-        <f>MONTH(B27)</f>
+        <f t="shared" si="1"/>
         <v>7</v>
       </c>
       <c r="E27" s="15">
-        <f>DAY(B27)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
@@ -1490,15 +3511,15 @@
         <v>37304</v>
       </c>
       <c r="C28" s="15">
-        <f>YEAR(B28)</f>
+        <f t="shared" si="0"/>
         <v>2002</v>
       </c>
       <c r="D28" s="13">
-        <f>MONTH(B28)</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E28" s="15">
-        <f>DAY(B28)</f>
+        <f t="shared" si="2"/>
         <v>17</v>
       </c>
     </row>
@@ -1510,15 +3531,15 @@
         <v>37757</v>
       </c>
       <c r="C29" s="15">
-        <f>YEAR(B29)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D29" s="13">
-        <f>MONTH(B29)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="E29" s="15">
-        <f>DAY(B29)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -1530,15 +3551,15 @@
         <v>38458</v>
       </c>
       <c r="C30" s="15">
-        <f>YEAR(B30)</f>
+        <f t="shared" si="0"/>
         <v>2005</v>
       </c>
       <c r="D30" s="13">
-        <f>MONTH(B30)</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="E30" s="15">
-        <f>DAY(B30)</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -1550,15 +3571,15 @@
         <v>38275</v>
       </c>
       <c r="C31" s="15">
-        <f>YEAR(B31)</f>
+        <f t="shared" si="0"/>
         <v>2004</v>
       </c>
       <c r="D31" s="13">
-        <f>MONTH(B31)</f>
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="E31" s="15">
-        <f>DAY(B31)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1570,15 +3591,15 @@
         <v>37970</v>
       </c>
       <c r="C32" s="15">
-        <f>YEAR(B32)</f>
+        <f t="shared" si="0"/>
         <v>2003</v>
       </c>
       <c r="D32" s="13">
-        <f>MONTH(B32)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E32" s="15">
-        <f>DAY(B32)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1590,15 +3611,15 @@
         <v>37390</v>
       </c>
       <c r="C33" s="15">
-        <f>YEAR(B33)</f>
+        <f t="shared" si="0"/>
         <v>2002</v>
       </c>
       <c r="D33" s="13">
-        <f>MONTH(B33)</f>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
       <c r="E33" s="15">
-        <f>DAY(B33)</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1610,15 +3631,15 @@
         <v>36721</v>
       </c>
       <c r="C34" s="15">
-        <f>YEAR(B34)</f>
+        <f t="shared" ref="C34:C65" si="3">YEAR(B34)</f>
         <v>2000</v>
       </c>
       <c r="D34" s="13">
-        <f>MONTH(B34)</f>
+        <f t="shared" ref="D34:D54" si="4">MONTH(B34)</f>
         <v>7</v>
       </c>
       <c r="E34" s="15">
-        <f>DAY(B34)</f>
+        <f t="shared" ref="E34:E54" si="5">DAY(B34)</f>
         <v>14</v>
       </c>
     </row>
@@ -1630,15 +3651,15 @@
         <v>37665</v>
       </c>
       <c r="C35" s="15">
-        <f>YEAR(B35)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D35" s="13">
-        <f>MONTH(B35)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="E35" s="15">
-        <f>DAY(B35)</f>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
     </row>
@@ -1650,15 +3671,15 @@
         <v>37997</v>
       </c>
       <c r="C36" s="15">
-        <f>YEAR(B36)</f>
+        <f t="shared" si="3"/>
         <v>2004</v>
       </c>
       <c r="D36" s="13">
-        <f>MONTH(B36)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
       <c r="E36" s="15">
-        <f>DAY(B36)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
@@ -1670,15 +3691,15 @@
         <v>37298</v>
       </c>
       <c r="C37" s="15">
-        <f>YEAR(B37)</f>
+        <f t="shared" si="3"/>
         <v>2002</v>
       </c>
       <c r="D37" s="13">
-        <f>MONTH(B37)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="E37" s="15">
-        <f>DAY(B37)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
@@ -1690,15 +3711,15 @@
         <v>37601</v>
       </c>
       <c r="C38" s="15">
-        <f>YEAR(B38)</f>
+        <f t="shared" si="3"/>
         <v>2002</v>
       </c>
       <c r="D38" s="13">
-        <f>MONTH(B38)</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="E38" s="15">
-        <f>DAY(B38)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
@@ -1710,15 +3731,15 @@
         <v>38028</v>
       </c>
       <c r="C39" s="15">
-        <f>YEAR(B39)</f>
+        <f t="shared" si="3"/>
         <v>2004</v>
       </c>
       <c r="D39" s="13">
-        <f>MONTH(B39)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="E39" s="15">
-        <f>DAY(B39)</f>
+        <f t="shared" si="5"/>
         <v>11</v>
       </c>
     </row>
@@ -1730,15 +3751,15 @@
         <v>37965</v>
       </c>
       <c r="C40" s="15">
-        <f>YEAR(B40)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D40" s="13">
-        <f>MONTH(B40)</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="E40" s="15">
-        <f>DAY(B40)</f>
+        <f t="shared" si="5"/>
         <v>10</v>
       </c>
     </row>
@@ -1750,15 +3771,15 @@
         <v>37536</v>
       </c>
       <c r="C41" s="15">
-        <f>YEAR(B41)</f>
+        <f t="shared" si="3"/>
         <v>2002</v>
       </c>
       <c r="D41" s="13">
-        <f>MONTH(B41)</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="E41" s="15">
-        <f>DAY(B41)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -1770,15 +3791,15 @@
         <v>37748</v>
       </c>
       <c r="C42" s="15">
-        <f>YEAR(B42)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D42" s="13">
-        <f>MONTH(B42)</f>
+        <f t="shared" si="4"/>
         <v>5</v>
       </c>
       <c r="E42" s="15">
-        <f>DAY(B42)</f>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
     </row>
@@ -1790,15 +3811,15 @@
         <v>38023</v>
       </c>
       <c r="C43" s="15">
-        <f>YEAR(B43)</f>
+        <f t="shared" si="3"/>
         <v>2004</v>
       </c>
       <c r="D43" s="13">
-        <f>MONTH(B43)</f>
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
       <c r="E43" s="15">
-        <f>DAY(B43)</f>
+        <f t="shared" si="5"/>
         <v>6</v>
       </c>
     </row>
@@ -1810,15 +3831,15 @@
         <v>38296</v>
       </c>
       <c r="C44" s="15">
-        <f>YEAR(B44)</f>
+        <f t="shared" si="3"/>
         <v>2004</v>
       </c>
       <c r="D44" s="13">
-        <f>MONTH(B44)</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="E44" s="15">
-        <f>DAY(B44)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -1830,15 +3851,15 @@
         <v>37442</v>
       </c>
       <c r="C45" s="15">
-        <f>YEAR(B45)</f>
+        <f t="shared" si="3"/>
         <v>2002</v>
       </c>
       <c r="D45" s="13">
-        <f>MONTH(B45)</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E45" s="15">
-        <f>DAY(B45)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -1850,15 +3871,15 @@
         <v>38235</v>
       </c>
       <c r="C46" s="15">
-        <f>YEAR(B46)</f>
+        <f t="shared" si="3"/>
         <v>2004</v>
       </c>
       <c r="D46" s="13">
-        <f>MONTH(B46)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="E46" s="15">
-        <f>DAY(B46)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -1870,15 +3891,15 @@
         <v>37473</v>
       </c>
       <c r="C47" s="15">
-        <f>YEAR(B47)</f>
+        <f t="shared" si="3"/>
         <v>2002</v>
       </c>
       <c r="D47" s="13">
-        <f>MONTH(B47)</f>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="E47" s="15">
-        <f>DAY(B47)</f>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
     </row>
@@ -1890,15 +3911,15 @@
         <v>37929</v>
       </c>
       <c r="C48" s="15">
-        <f>YEAR(B48)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D48" s="13">
-        <f>MONTH(B48)</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="E48" s="15">
-        <f>DAY(B48)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
@@ -1910,15 +3931,15 @@
         <v>37806</v>
       </c>
       <c r="C49" s="15">
-        <f>YEAR(B49)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D49" s="13">
-        <f>MONTH(B49)</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="E49" s="15">
-        <f>DAY(B49)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
@@ -1930,15 +3951,15 @@
         <v>37503</v>
       </c>
       <c r="C50" s="15">
-        <f>YEAR(B50)</f>
+        <f t="shared" si="3"/>
         <v>2002</v>
       </c>
       <c r="D50" s="13">
-        <f>MONTH(B50)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="E50" s="15">
-        <f>DAY(B50)</f>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
     </row>
@@ -1950,15 +3971,15 @@
         <v>37714</v>
       </c>
       <c r="C51" s="15">
-        <f>YEAR(B51)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D51" s="13">
-        <f>MONTH(B51)</f>
+        <f t="shared" si="4"/>
         <v>4</v>
       </c>
       <c r="E51" s="15">
-        <f>DAY(B51)</f>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
     </row>
@@ -1970,15 +3991,15 @@
         <v>37957</v>
       </c>
       <c r="C52" s="15">
-        <f>YEAR(B52)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D52" s="13">
-        <f>MONTH(B52)</f>
+        <f t="shared" si="4"/>
         <v>12</v>
       </c>
       <c r="E52" s="15">
-        <f>DAY(B52)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -1990,15 +4011,15 @@
         <v>37866</v>
       </c>
       <c r="C53" s="15">
-        <f>YEAR(B53)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D53" s="13">
-        <f>MONTH(B53)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="E53" s="15">
-        <f>DAY(B53)</f>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
@@ -2010,15 +4031,15 @@
         <v>37865</v>
       </c>
       <c r="C54" s="15">
-        <f>YEAR(B54)</f>
+        <f t="shared" si="3"/>
         <v>2003</v>
       </c>
       <c r="D54" s="13">
-        <f>MONTH(B54)</f>
+        <f t="shared" si="4"/>
         <v>9</v>
       </c>
       <c r="E54" s="15">
-        <f>DAY(B54)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
@@ -5909,11 +7930,11 @@
       </c>
       <c r="D2" s="15">
         <f ca="1">DATEDIF(B2,TODAY(),"m")</f>
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E2" s="10">
         <f ca="1">DATEDIF(B2,TODAY(),"D")</f>
-        <v>8369</v>
+        <v>8371</v>
       </c>
       <c r="H2" t="s">
         <v>87</v>
@@ -5932,11 +7953,11 @@
       </c>
       <c r="D3" s="15">
         <f t="shared" ref="D3:D54" ca="1" si="1">DATEDIF(B3,TODAY(),"m")</f>
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E3" s="10">
         <f t="shared" ref="E3:E54" ca="1" si="2">DATEDIF(B3,TODAY(),"D")</f>
-        <v>9099</v>
+        <v>9101</v>
       </c>
       <c r="H3" t="s">
         <v>88</v>
@@ -5955,11 +7976,11 @@
       </c>
       <c r="D4" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E4" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8462</v>
+        <v>8464</v>
       </c>
       <c r="H4" t="s">
         <v>89</v>
@@ -5978,11 +7999,11 @@
       </c>
       <c r="D5" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E5" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8584</v>
+        <v>8586</v>
       </c>
       <c r="H5" t="s">
         <v>90</v>
@@ -6001,11 +8022,11 @@
       </c>
       <c r="D6" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E6" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8004</v>
+        <v>8006</v>
       </c>
       <c r="H6" t="s">
         <v>91</v>
@@ -6024,11 +8045,11 @@
       </c>
       <c r="D7" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E7" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7943</v>
+        <v>7945</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -6048,7 +8069,7 @@
       </c>
       <c r="E8" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8401</v>
+        <v>8403</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -6068,7 +8089,7 @@
       </c>
       <c r="E9" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7945</v>
+        <v>7947</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -6088,7 +8109,7 @@
       </c>
       <c r="E10" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>9011</v>
+        <v>9013</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -6108,7 +8129,7 @@
       </c>
       <c r="E11" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7886</v>
+        <v>7888</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -6128,7 +8149,7 @@
       </c>
       <c r="E12" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8590</v>
+        <v>8592</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -6148,27 +8169,27 @@
       </c>
       <c r="E13" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8468</v>
+        <v>8470</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="B14" s="12">
+      <c r="B14" s="25">
         <v>37126</v>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="26">
         <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="26">
         <f t="shared" ca="1" si="1"/>
         <v>301</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="27">
         <f t="shared" ca="1" si="2"/>
-        <v>9168</v>
+        <v>9170</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -6188,7 +8209,7 @@
       </c>
       <c r="E15" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8591</v>
+        <v>8593</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="15.5" x14ac:dyDescent="0.35">
@@ -6208,7 +8229,7 @@
       </c>
       <c r="E16" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8650</v>
+        <v>8652</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6228,7 +8249,7 @@
       </c>
       <c r="E17" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8956</v>
+        <v>8958</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6248,7 +8269,7 @@
       </c>
       <c r="E18" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8225</v>
+        <v>8227</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6268,7 +8289,7 @@
       </c>
       <c r="E19" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8500</v>
+        <v>8502</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6288,7 +8309,7 @@
       </c>
       <c r="E20" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8134</v>
+        <v>8136</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6308,7 +8329,7 @@
       </c>
       <c r="E21" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8105</v>
+        <v>8107</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6328,7 +8349,7 @@
       </c>
       <c r="E22" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7982</v>
+        <v>7984</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6348,7 +8369,7 @@
       </c>
       <c r="E23" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8747</v>
+        <v>8749</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6368,7 +8389,7 @@
       </c>
       <c r="E24" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7834</v>
+        <v>7836</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6388,7 +8409,7 @@
       </c>
       <c r="E25" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7865</v>
+        <v>7867</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6408,7 +8429,7 @@
       </c>
       <c r="E26" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7866</v>
+        <v>7868</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6428,7 +8449,7 @@
       </c>
       <c r="E27" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8109</v>
+        <v>8111</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6448,7 +8469,7 @@
       </c>
       <c r="E28" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8990</v>
+        <v>8992</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6468,7 +8489,7 @@
       </c>
       <c r="E29" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8537</v>
+        <v>8539</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6488,7 +8509,7 @@
       </c>
       <c r="E30" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7836</v>
+        <v>7838</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6508,7 +8529,7 @@
       </c>
       <c r="E31" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8019</v>
+        <v>8021</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6528,7 +8549,7 @@
       </c>
       <c r="E32" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8324</v>
+        <v>8326</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6548,7 +8569,7 @@
       </c>
       <c r="E33" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8904</v>
+        <v>8906</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6568,7 +8589,7 @@
       </c>
       <c r="E34" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>9573</v>
+        <v>9575</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6588,7 +8609,7 @@
       </c>
       <c r="E35" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8629</v>
+        <v>8631</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6608,7 +8629,7 @@
       </c>
       <c r="E36" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8297</v>
+        <v>8299</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6628,7 +8649,7 @@
       </c>
       <c r="E37" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8996</v>
+        <v>8998</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6648,7 +8669,7 @@
       </c>
       <c r="E38" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8693</v>
+        <v>8695</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6668,7 +8689,7 @@
       </c>
       <c r="E39" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8266</v>
+        <v>8268</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6688,7 +8709,7 @@
       </c>
       <c r="E40" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8329</v>
+        <v>8331</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6708,7 +8729,7 @@
       </c>
       <c r="E41" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8758</v>
+        <v>8760</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6728,7 +8749,7 @@
       </c>
       <c r="E42" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8546</v>
+        <v>8548</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6748,7 +8769,7 @@
       </c>
       <c r="E43" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8271</v>
+        <v>8273</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6768,7 +8789,7 @@
       </c>
       <c r="E44" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>7998</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6788,7 +8809,7 @@
       </c>
       <c r="E45" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8852</v>
+        <v>8854</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6808,7 +8829,7 @@
       </c>
       <c r="E46" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8059</v>
+        <v>8061</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6828,7 +8849,7 @@
       </c>
       <c r="E47" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8821</v>
+        <v>8823</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6848,7 +8869,7 @@
       </c>
       <c r="E48" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8365</v>
+        <v>8367</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6868,7 +8889,7 @@
       </c>
       <c r="E49" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8488</v>
+        <v>8490</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6888,7 +8909,7 @@
       </c>
       <c r="E50" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8791</v>
+        <v>8793</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6908,7 +8929,7 @@
       </c>
       <c r="E51" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8580</v>
+        <v>8582</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6928,7 +8949,7 @@
       </c>
       <c r="E52" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8337</v>
+        <v>8339</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6948,7 +8969,7 @@
       </c>
       <c r="E53" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8428</v>
+        <v>8430</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -6964,15 +8985,1326 @@
       </c>
       <c r="D54" s="15">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E54" s="10">
         <f t="shared" ca="1" si="2"/>
-        <v>8429</v>
+        <v>8431</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4667327-BA9B-4107-9010-716308D8138B}">
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="39" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.81640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.1796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="28">
+        <v>37126</v>
+      </c>
+      <c r="C2" s="15">
+        <f ca="1">DATEDIF(B2,TODAY(),"Y")</f>
+        <v>25</v>
+      </c>
+      <c r="D2" s="15">
+        <f ca="1">DATEDIF(B2,TODAY(),"YM")</f>
+        <v>1</v>
+      </c>
+      <c r="E2" s="15">
+        <f ca="1">DATEDIF(B2,TODAY(),"MD")</f>
+        <v>8</v>
+      </c>
+      <c r="F2" s="15" t="str">
+        <f ca="1">_xlfn.CONCAT(C2," Years ",D2, " months ",E2, " Days Old")</f>
+        <v>25 Years 1 months 8 Days Old</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="30">
+        <v>37925</v>
+      </c>
+      <c r="C3" s="15">
+        <f t="shared" ref="C3:C54" ca="1" si="0">DATEDIF(B3,TODAY(),"Y")</f>
+        <v>22</v>
+      </c>
+      <c r="D3" s="15">
+        <f t="shared" ref="D3:D54" ca="1" si="1">DATEDIF(B3,TODAY(),"YM")</f>
+        <v>11</v>
+      </c>
+      <c r="E3" s="15">
+        <f t="shared" ref="E3:E54" ca="1" si="2">DATEDIF(B3,TODAY(),"MD")</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="15" t="str">
+        <f t="shared" ref="F3:F54" ca="1" si="3">_xlfn.CONCAT(C3," Years ",D3, " months ",E3, " Days Old")</f>
+        <v>22 Years 11 months 0 Days Old</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="30">
+        <v>37195</v>
+      </c>
+      <c r="C4" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D4" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="E4" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F4" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 11 months 0 Days Old</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="30">
+        <v>37832</v>
+      </c>
+      <c r="C5" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D5" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E5" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F5" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 2 months 1 Days Old</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="30">
+        <v>37710</v>
+      </c>
+      <c r="C6" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D6" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E6" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F6" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 6 months 1 Days Old</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="30">
+        <v>38290</v>
+      </c>
+      <c r="C7" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D7" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="E7" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F7" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 11 months 1 Days Old</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="30">
+        <v>38351</v>
+      </c>
+      <c r="C8" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D8" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E8" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F8" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 9 months 1 Days Old</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" s="30">
+        <v>37893</v>
+      </c>
+      <c r="C9" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D9" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E9" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="F9" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 0 months 2 Days Old</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="30">
+        <v>38349</v>
+      </c>
+      <c r="C10" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D10" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E10" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>3</v>
+      </c>
+      <c r="F10" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 9 months 3 Days Old</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="30">
+        <v>37283</v>
+      </c>
+      <c r="C11" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D11" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="E11" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F11" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 8 months 4 Days Old</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="30">
+        <v>38408</v>
+      </c>
+      <c r="C12" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D12" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E12" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>6</v>
+      </c>
+      <c r="F12" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 7 months 6 Days Old</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="30">
+        <v>37704</v>
+      </c>
+      <c r="C13" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D13" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E13" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F13" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 6 months 7 Days Old</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="30">
+        <v>37826</v>
+      </c>
+      <c r="C14" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D14" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E14" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>7</v>
+      </c>
+      <c r="F14" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 2 months 7 Days Old</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="30">
+        <v>37703</v>
+      </c>
+      <c r="C15" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D15" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E15" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F15" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 6 months 8 Days Old</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="30">
+        <v>37644</v>
+      </c>
+      <c r="C16" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D16" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="E16" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F16" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 8 months 8 Days Old</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="30">
+        <v>37338</v>
+      </c>
+      <c r="C17" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D17" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E17" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F17" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 6 months 8 Days Old</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="30">
+        <v>38069</v>
+      </c>
+      <c r="C18" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D18" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E18" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F18" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 6 months 8 Days Old</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="30">
+        <v>37794</v>
+      </c>
+      <c r="C19" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D19" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E19" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="F19" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 3 months 9 Days Old</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="30">
+        <v>38160</v>
+      </c>
+      <c r="C20" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D20" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="F20" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 3 months 9 Days Old</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" s="30">
+        <v>38189</v>
+      </c>
+      <c r="C21" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D21" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E21" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F21" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 2 months 10 Days Old</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="30">
+        <v>38312</v>
+      </c>
+      <c r="C22" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D22" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E22" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F22" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 10 months 10 Days Old</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="30">
+        <v>37547</v>
+      </c>
+      <c r="C23" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D23" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="F23" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 11 months 13 Days Old</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="30">
+        <v>38460</v>
+      </c>
+      <c r="C24" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D24" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="E24" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="F24" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 5 months 13 Days Old</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="29" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="30">
+        <v>38429</v>
+      </c>
+      <c r="C25" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D25" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E25" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>13</v>
+      </c>
+      <c r="F25" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 6 months 13 Days Old</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="30">
+        <v>38428</v>
+      </c>
+      <c r="C26" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D26" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E26" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="F26" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 6 months 14 Days Old</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B27" s="30">
+        <v>38185</v>
+      </c>
+      <c r="C27" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D27" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="F27" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 2 months 14 Days Old</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="B28" s="30">
+        <v>37304</v>
+      </c>
+      <c r="C28" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D28" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E28" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="F28" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 7 months 14 Days Old</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="30">
+        <v>37757</v>
+      </c>
+      <c r="C29" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D29" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E29" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="F29" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 4 months 15 Days Old</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="30">
+        <v>38458</v>
+      </c>
+      <c r="C30" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D30" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="E30" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>15</v>
+      </c>
+      <c r="F30" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 5 months 15 Days Old</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="30">
+        <v>38275</v>
+      </c>
+      <c r="C31" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D31" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="E31" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="F31" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 11 months 16 Days Old</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="30">
+        <v>37970</v>
+      </c>
+      <c r="C32" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D32" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E32" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="F32" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 9 months 16 Days Old</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="30">
+        <v>37390</v>
+      </c>
+      <c r="C33" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D33" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E33" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="F33" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 4 months 17 Days Old</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="30">
+        <v>36721</v>
+      </c>
+      <c r="C34" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="D34" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E34" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>17</v>
+      </c>
+      <c r="F34" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>26 Years 2 months 17 Days Old</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="30">
+        <v>37665</v>
+      </c>
+      <c r="C35" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D35" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E35" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>18</v>
+      </c>
+      <c r="F35" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 7 months 18 Days Old</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="30">
+        <v>37997</v>
+      </c>
+      <c r="C36" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D36" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="E36" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F36" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 8 months 20 Days Old</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="30">
+        <v>37298</v>
+      </c>
+      <c r="C37" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D37" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E37" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F37" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 7 months 20 Days Old</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="30">
+        <v>37601</v>
+      </c>
+      <c r="C38" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D38" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E38" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F38" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 9 months 20 Days Old</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="30">
+        <v>38028</v>
+      </c>
+      <c r="C39" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D39" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E39" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="F39" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 7 months 20 Days Old</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="30">
+        <v>37965</v>
+      </c>
+      <c r="C40" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D40" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E40" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>21</v>
+      </c>
+      <c r="F40" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 9 months 21 Days Old</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" s="30">
+        <v>37536</v>
+      </c>
+      <c r="C41" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D41" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>11</v>
+      </c>
+      <c r="E41" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="F41" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 11 months 24 Days Old</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B42" s="30">
+        <v>37748</v>
+      </c>
+      <c r="C42" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D42" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E42" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>24</v>
+      </c>
+      <c r="F42" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 4 months 24 Days Old</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="30">
+        <v>38023</v>
+      </c>
+      <c r="C43" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D43" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="E43" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="F43" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 7 months 25 Days Old</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="30">
+        <v>38296</v>
+      </c>
+      <c r="C44" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="D44" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E44" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="F44" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>21 Years 10 months 26 Days Old</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="30">
+        <v>37442</v>
+      </c>
+      <c r="C45" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D45" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E45" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="F45" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 2 months 26 Days Old</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="30">
+        <v>38235</v>
+      </c>
+      <c r="C46" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D46" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E46" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="F46" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 0 months 26 Days Old</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B47" s="30">
+        <v>37473</v>
+      </c>
+      <c r="C47" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D47" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E47" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>26</v>
+      </c>
+      <c r="F47" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 1 months 26 Days Old</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="30">
+        <v>37929</v>
+      </c>
+      <c r="C48" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D48" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="E48" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="F48" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 10 months 27 Days Old</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="30">
+        <v>37806</v>
+      </c>
+      <c r="C49" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D49" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E49" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="F49" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 2 months 27 Days Old</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="30">
+        <v>37503</v>
+      </c>
+      <c r="C50" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="D50" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E50" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>27</v>
+      </c>
+      <c r="F50" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>24 Years 0 months 27 Days Old</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="B51" s="30">
+        <v>37714</v>
+      </c>
+      <c r="C51" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D51" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="E51" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>28</v>
+      </c>
+      <c r="F51" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 5 months 28 Days Old</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="30">
+        <v>37957</v>
+      </c>
+      <c r="C52" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="D52" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E52" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="F52" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>22 Years 9 months 29 Days Old</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="B53" s="30">
+        <v>37866</v>
+      </c>
+      <c r="C53" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D53" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="E53" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>29</v>
+      </c>
+      <c r="F53" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 0 months 29 Days Old</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="29" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="30">
+        <v>37865</v>
+      </c>
+      <c r="C54" s="15">
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="D54" s="15">
+        <f t="shared" ca="1" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E54" s="15">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="15" t="str">
+        <f t="shared" ca="1" si="3"/>
+        <v>23 Years 1 months 0 Days Old</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Excel/DateFunctions8001.xlsx
+++ b/Excel/DateFunctions8001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C90554C8-A9AF-4F84-A5FB-94BB6C0AC491}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476BD5EC-E646-4624-B167-A6910FB08FAE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="7" xr2:uid="{FFAF0F3A-FACC-44CD-90E3-6CA7DF844403}"/>
   </bookViews>
@@ -23,6 +23,7 @@
     <sheet name="AgeCalculation" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">AgeCalculation!$H$1:$H$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">YearMonthDay!$A$1:$E$54</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="94">
   <si>
     <t>EmployeeNam</t>
   </si>
@@ -315,6 +316,9 @@
   <si>
     <t>FinalResult</t>
   </si>
+  <si>
+    <t>Bonus</t>
+  </si>
 </sst>
 </file>
 
@@ -462,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -524,11 +528,20 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2935,7 +2948,7 @@
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="6">
         <f ca="1">NOW()</f>
-        <v>46296.474531250002</v>
+        <v>46296.479978819443</v>
       </c>
     </row>
   </sheetData>
@@ -9000,10 +9013,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4667327-BA9B-4107-9010-716308D8138B}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="39" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39" style="33" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.90625" style="2" bestFit="1" customWidth="1"/>
@@ -9012,8 +9025,8 @@
     <col min="7" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="30" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="14" t="s">
@@ -9031,9 +9044,12 @@
       <c r="F1" s="14" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="H1" s="14" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="31" t="s">
         <v>61</v>
       </c>
       <c r="B2" s="28">
@@ -9055,12 +9071,23 @@
         <f ca="1">_xlfn.CONCAT(C2," Years ",D2, " months ",E2, " Days Old")</f>
         <v>25 Years 1 months 8 Days Old</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="29" t="s">
+      <c r="H2" s="15">
+        <f ca="1">DATEDIF(B2,TODAY(),"YD")</f>
+        <v>39</v>
+      </c>
+      <c r="I2" s="2">
+        <v>365</v>
+      </c>
+      <c r="J2" s="2">
+        <f ca="1">I2-H2</f>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="29">
         <v>37925</v>
       </c>
       <c r="C3" s="15">
@@ -9079,12 +9106,23 @@
         <f t="shared" ref="F3:F54" ca="1" si="3">_xlfn.CONCAT(C3," Years ",D3, " months ",E3, " Days Old")</f>
         <v>22 Years 11 months 0 Days Old</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="29" t="s">
+      <c r="H3" s="15">
+        <f t="shared" ref="H3:H54" ca="1" si="4">DATEDIF(B3,TODAY(),"YD")</f>
+        <v>336</v>
+      </c>
+      <c r="I3" s="2">
+        <v>365</v>
+      </c>
+      <c r="J3" s="2">
+        <f t="shared" ref="J3:J54" ca="1" si="5">I3-H3</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="29">
         <v>37195</v>
       </c>
       <c r="C4" s="15">
@@ -9103,12 +9141,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 11 months 0 Days Old</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="29" t="s">
+      <c r="H4" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>335</v>
+      </c>
+      <c r="I4" s="2">
+        <v>365</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="29">
         <v>37832</v>
       </c>
       <c r="C5" s="15">
@@ -9127,12 +9176,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 2 months 1 Days Old</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="29" t="s">
+      <c r="H5" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>63</v>
+      </c>
+      <c r="I5" s="2">
+        <v>365</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="29">
         <v>37710</v>
       </c>
       <c r="C6" s="15">
@@ -9151,12 +9211,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 6 months 1 Days Old</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="29" t="s">
+      <c r="H6" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>185</v>
+      </c>
+      <c r="I6" s="2">
+        <v>365</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>38290</v>
       </c>
       <c r="C7" s="15">
@@ -9175,12 +9246,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 11 months 1 Days Old</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="29" t="s">
+      <c r="H7" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>336</v>
+      </c>
+      <c r="I7" s="2">
+        <v>365</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>38351</v>
       </c>
       <c r="C8" s="15">
@@ -9199,12 +9281,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 9 months 1 Days Old</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="29" t="s">
+      <c r="H8" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>275</v>
+      </c>
+      <c r="I8" s="2">
+        <v>365</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>37893</v>
       </c>
       <c r="C9" s="15">
@@ -9223,12 +9316,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 0 months 2 Days Old</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="29" t="s">
+      <c r="H9" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I9" s="2">
+        <v>365</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>363</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="29">
         <v>38349</v>
       </c>
       <c r="C10" s="15">
@@ -9247,12 +9351,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 9 months 3 Days Old</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A11" s="29" t="s">
+      <c r="H10" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>277</v>
+      </c>
+      <c r="I10" s="2">
+        <v>365</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <v>37283</v>
       </c>
       <c r="C11" s="15">
@@ -9271,12 +9386,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 8 months 4 Days Old</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A12" s="29" t="s">
+      <c r="H11" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>247</v>
+      </c>
+      <c r="I11" s="2">
+        <v>365</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="29">
         <v>38408</v>
       </c>
       <c r="C12" s="15">
@@ -9295,12 +9421,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 7 months 6 Days Old</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A13" s="29" t="s">
+      <c r="H12" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>218</v>
+      </c>
+      <c r="I12" s="2">
+        <v>365</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <v>37704</v>
       </c>
       <c r="C13" s="15">
@@ -9319,12 +9456,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 6 months 7 Days Old</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A14" s="29" t="s">
+      <c r="H13" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>191</v>
+      </c>
+      <c r="I13" s="2">
+        <v>365</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="29">
         <v>37826</v>
       </c>
       <c r="C14" s="15">
@@ -9343,12 +9491,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 2 months 7 Days Old</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A15" s="29" t="s">
+      <c r="H14" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>69</v>
+      </c>
+      <c r="I14" s="2">
+        <v>365</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>296</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="29">
         <v>37703</v>
       </c>
       <c r="C15" s="15">
@@ -9367,12 +9526,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 6 months 8 Days Old</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A16" s="29" t="s">
+      <c r="H15" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="I15" s="2">
+        <v>365</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>37644</v>
       </c>
       <c r="C16" s="15">
@@ -9391,12 +9561,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 8 months 8 Days Old</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="29" t="s">
+      <c r="H16" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>251</v>
+      </c>
+      <c r="I16" s="2">
+        <v>365</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="29">
         <v>37338</v>
       </c>
       <c r="C17" s="15">
@@ -9415,12 +9596,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 6 months 8 Days Old</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A18" s="29" t="s">
+      <c r="H17" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="I17" s="2">
+        <v>365</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="29">
         <v>38069</v>
       </c>
       <c r="C18" s="15">
@@ -9439,12 +9631,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 6 months 8 Days Old</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A19" s="29" t="s">
+      <c r="H18" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>192</v>
+      </c>
+      <c r="I18" s="2">
+        <v>365</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="29">
         <v>37794</v>
       </c>
       <c r="C19" s="15">
@@ -9463,12 +9666,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 3 months 9 Days Old</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="29" t="s">
+      <c r="H19" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>101</v>
+      </c>
+      <c r="I19" s="2">
+        <v>365</v>
+      </c>
+      <c r="J19" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A20" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="29">
         <v>38160</v>
       </c>
       <c r="C20" s="15">
@@ -9487,12 +9701,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 3 months 9 Days Old</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A21" s="29" t="s">
+      <c r="H20" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>101</v>
+      </c>
+      <c r="I20" s="2">
+        <v>365</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A21" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="29">
         <v>38189</v>
       </c>
       <c r="C21" s="15">
@@ -9511,12 +9736,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 2 months 10 Days Old</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A22" s="29" t="s">
+      <c r="H21" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>72</v>
+      </c>
+      <c r="I21" s="2">
+        <v>365</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="29">
         <v>38312</v>
       </c>
       <c r="C22" s="15">
@@ -9535,12 +9771,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 10 months 10 Days Old</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="29" t="s">
+      <c r="H22" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>314</v>
+      </c>
+      <c r="I22" s="2">
+        <v>365</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A23" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="30">
+      <c r="B23" s="29">
         <v>37547</v>
       </c>
       <c r="C23" s="15">
@@ -9559,12 +9806,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 11 months 13 Days Old</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="29" t="s">
+      <c r="H23" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>348</v>
+      </c>
+      <c r="I23" s="2">
+        <v>365</v>
+      </c>
+      <c r="J23" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A24" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="29">
         <v>38460</v>
       </c>
       <c r="C24" s="15">
@@ -9583,12 +9841,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 5 months 13 Days Old</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="29" t="s">
+      <c r="H24" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>166</v>
+      </c>
+      <c r="I24" s="2">
+        <v>365</v>
+      </c>
+      <c r="J24" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="29">
         <v>38429</v>
       </c>
       <c r="C25" s="15">
@@ -9607,12 +9876,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 6 months 13 Days Old</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="29" t="s">
+      <c r="H25" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>197</v>
+      </c>
+      <c r="I25" s="2">
+        <v>365</v>
+      </c>
+      <c r="J25" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="29">
         <v>38428</v>
       </c>
       <c r="C26" s="15">
@@ -9631,12 +9911,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 6 months 14 Days Old</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A27" s="29" t="s">
+      <c r="H26" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>198</v>
+      </c>
+      <c r="I26" s="2">
+        <v>365</v>
+      </c>
+      <c r="J26" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="29">
         <v>38185</v>
       </c>
       <c r="C27" s="15">
@@ -9655,12 +9946,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 2 months 14 Days Old</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A28" s="29" t="s">
+      <c r="H27" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>76</v>
+      </c>
+      <c r="I27" s="2">
+        <v>365</v>
+      </c>
+      <c r="J27" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="30">
+      <c r="B28" s="29">
         <v>37304</v>
       </c>
       <c r="C28" s="15">
@@ -9679,12 +9981,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 7 months 14 Days Old</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="29" t="s">
+      <c r="H28" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>226</v>
+      </c>
+      <c r="I28" s="2">
+        <v>365</v>
+      </c>
+      <c r="J28" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="29">
         <v>37757</v>
       </c>
       <c r="C29" s="15">
@@ -9703,12 +10016,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 4 months 15 Days Old</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="29" t="s">
+      <c r="H29" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>138</v>
+      </c>
+      <c r="I29" s="2">
+        <v>365</v>
+      </c>
+      <c r="J29" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>227</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A30" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="29">
         <v>38458</v>
       </c>
       <c r="C30" s="15">
@@ -9727,12 +10051,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 5 months 15 Days Old</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="29" t="s">
+      <c r="H30" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>168</v>
+      </c>
+      <c r="I30" s="2">
+        <v>365</v>
+      </c>
+      <c r="J30" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A31" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="29">
         <v>38275</v>
       </c>
       <c r="C31" s="15">
@@ -9751,12 +10086,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 11 months 16 Days Old</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A32" s="29" t="s">
+      <c r="H31" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>351</v>
+      </c>
+      <c r="I31" s="2">
+        <v>365</v>
+      </c>
+      <c r="J31" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="29">
         <v>37970</v>
       </c>
       <c r="C32" s="15">
@@ -9775,12 +10121,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 9 months 16 Days Old</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="29" t="s">
+      <c r="H32" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>291</v>
+      </c>
+      <c r="I32" s="2">
+        <v>365</v>
+      </c>
+      <c r="J32" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="B33" s="30">
+      <c r="B33" s="29">
         <v>37390</v>
       </c>
       <c r="C33" s="15">
@@ -9799,12 +10156,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 4 months 17 Days Old</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="29" t="s">
+      <c r="H33" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>140</v>
+      </c>
+      <c r="I33" s="2">
+        <v>365</v>
+      </c>
+      <c r="J33" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>225</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="32" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="30">
+      <c r="B34" s="29">
         <v>36721</v>
       </c>
       <c r="C34" s="15">
@@ -9823,12 +10191,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>26 Years 2 months 17 Days Old</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="29" t="s">
+      <c r="H34" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>79</v>
+      </c>
+      <c r="I34" s="2">
+        <v>365</v>
+      </c>
+      <c r="J34" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>286</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <v>37665</v>
       </c>
       <c r="C35" s="15">
@@ -9847,12 +10226,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 7 months 18 Days Old</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="29" t="s">
+      <c r="H35" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>230</v>
+      </c>
+      <c r="I35" s="2">
+        <v>365</v>
+      </c>
+      <c r="J35" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A36" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="29">
         <v>37997</v>
       </c>
       <c r="C36" s="15">
@@ -9871,12 +10261,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 8 months 20 Days Old</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="29" t="s">
+      <c r="H36" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>264</v>
+      </c>
+      <c r="I36" s="2">
+        <v>365</v>
+      </c>
+      <c r="J36" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A37" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <v>37298</v>
       </c>
       <c r="C37" s="15">
@@ -9895,12 +10296,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 7 months 20 Days Old</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A38" s="29" t="s">
+      <c r="H37" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>232</v>
+      </c>
+      <c r="I37" s="2">
+        <v>365</v>
+      </c>
+      <c r="J37" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="30">
+      <c r="B38" s="29">
         <v>37601</v>
       </c>
       <c r="C38" s="15">
@@ -9919,12 +10331,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 9 months 20 Days Old</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="29" t="s">
+      <c r="H38" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>294</v>
+      </c>
+      <c r="I38" s="2">
+        <v>365</v>
+      </c>
+      <c r="J38" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A39" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="30">
+      <c r="B39" s="29">
         <v>38028</v>
       </c>
       <c r="C39" s="15">
@@ -9943,12 +10366,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 7 months 20 Days Old</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A40" s="29" t="s">
+      <c r="H39" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>233</v>
+      </c>
+      <c r="I39" s="2">
+        <v>365</v>
+      </c>
+      <c r="J39" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A40" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="30">
+      <c r="B40" s="29">
         <v>37965</v>
       </c>
       <c r="C40" s="15">
@@ -9967,12 +10401,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 9 months 21 Days Old</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A41" s="29" t="s">
+      <c r="H40" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>296</v>
+      </c>
+      <c r="I40" s="2">
+        <v>365</v>
+      </c>
+      <c r="J40" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A41" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="B41" s="30">
+      <c r="B41" s="29">
         <v>37536</v>
       </c>
       <c r="C41" s="15">
@@ -9991,12 +10436,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 11 months 24 Days Old</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A42" s="29" t="s">
+      <c r="H41" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>359</v>
+      </c>
+      <c r="I41" s="2">
+        <v>365</v>
+      </c>
+      <c r="J41" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A42" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="29">
         <v>37748</v>
       </c>
       <c r="C42" s="15">
@@ -10015,12 +10471,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 4 months 24 Days Old</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A43" s="29" t="s">
+      <c r="H42" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>147</v>
+      </c>
+      <c r="I42" s="2">
+        <v>365</v>
+      </c>
+      <c r="J42" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A43" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="29">
         <v>38023</v>
       </c>
       <c r="C43" s="15">
@@ -10039,12 +10506,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 7 months 25 Days Old</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A44" s="29" t="s">
+      <c r="H43" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>238</v>
+      </c>
+      <c r="I43" s="2">
+        <v>365</v>
+      </c>
+      <c r="J43" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A44" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="B44" s="30">
+      <c r="B44" s="29">
         <v>38296</v>
       </c>
       <c r="C44" s="15">
@@ -10063,12 +10541,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>21 Years 10 months 26 Days Old</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A45" s="29" t="s">
+      <c r="H44" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>330</v>
+      </c>
+      <c r="I44" s="2">
+        <v>365</v>
+      </c>
+      <c r="J44" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A45" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="B45" s="30">
+      <c r="B45" s="29">
         <v>37442</v>
       </c>
       <c r="C45" s="15">
@@ -10087,12 +10576,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 2 months 26 Days Old</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A46" s="29" t="s">
+      <c r="H45" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>88</v>
+      </c>
+      <c r="I45" s="2">
+        <v>365</v>
+      </c>
+      <c r="J45" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>277</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A46" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="B46" s="30">
+      <c r="B46" s="29">
         <v>38235</v>
       </c>
       <c r="C46" s="15">
@@ -10111,12 +10611,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 0 months 26 Days Old</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A47" s="29" t="s">
+      <c r="H46" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>26</v>
+      </c>
+      <c r="I46" s="2">
+        <v>365</v>
+      </c>
+      <c r="J46" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A47" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="30">
+      <c r="B47" s="29">
         <v>37473</v>
       </c>
       <c r="C47" s="15">
@@ -10135,12 +10646,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 1 months 26 Days Old</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A48" s="29" t="s">
+      <c r="H47" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>57</v>
+      </c>
+      <c r="I47" s="2">
+        <v>365</v>
+      </c>
+      <c r="J47" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A48" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="30">
+      <c r="B48" s="29">
         <v>37929</v>
       </c>
       <c r="C48" s="15">
@@ -10159,12 +10681,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 10 months 27 Days Old</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A49" s="29" t="s">
+      <c r="H48" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>332</v>
+      </c>
+      <c r="I48" s="2">
+        <v>365</v>
+      </c>
+      <c r="J48" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A49" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="30">
+      <c r="B49" s="29">
         <v>37806</v>
       </c>
       <c r="C49" s="15">
@@ -10183,12 +10716,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 2 months 27 Days Old</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A50" s="29" t="s">
+      <c r="H49" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>89</v>
+      </c>
+      <c r="I49" s="2">
+        <v>365</v>
+      </c>
+      <c r="J49" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A50" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="30">
+      <c r="B50" s="29">
         <v>37503</v>
       </c>
       <c r="C50" s="15">
@@ -10207,12 +10751,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>24 Years 0 months 27 Days Old</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A51" s="29" t="s">
+      <c r="H50" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="I50" s="2">
+        <v>365</v>
+      </c>
+      <c r="J50" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>338</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A51" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="B51" s="30">
+      <c r="B51" s="29">
         <v>37714</v>
       </c>
       <c r="C51" s="15">
@@ -10231,12 +10786,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 5 months 28 Days Old</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A52" s="29" t="s">
+      <c r="H51" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>181</v>
+      </c>
+      <c r="I51" s="2">
+        <v>365</v>
+      </c>
+      <c r="J51" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A52" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="B52" s="30">
+      <c r="B52" s="29">
         <v>37957</v>
       </c>
       <c r="C52" s="15">
@@ -10255,12 +10821,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>22 Years 9 months 29 Days Old</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A53" s="29" t="s">
+      <c r="H52" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>304</v>
+      </c>
+      <c r="I52" s="2">
+        <v>365</v>
+      </c>
+      <c r="J52" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A53" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="B53" s="30">
+      <c r="B53" s="29">
         <v>37866</v>
       </c>
       <c r="C53" s="15">
@@ -10279,12 +10856,23 @@
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 0 months 29 Days Old</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A54" s="29" t="s">
+      <c r="H53" s="15">
+        <f t="shared" ca="1" si="4"/>
         <v>29</v>
       </c>
-      <c r="B54" s="30">
+      <c r="I53" s="2">
+        <v>365</v>
+      </c>
+      <c r="J53" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>336</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A54" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B54" s="29">
         <v>37865</v>
       </c>
       <c r="C54" s="15">
@@ -10302,6 +10890,17 @@
       <c r="F54" s="15" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>23 Years 1 months 0 Days Old</v>
+      </c>
+      <c r="H54" s="15">
+        <f t="shared" ca="1" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="I54" s="2">
+        <v>365</v>
+      </c>
+      <c r="J54" s="2">
+        <f t="shared" ca="1" si="5"/>
+        <v>335</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/DateFunctions8001.xlsx
+++ b/Excel/DateFunctions8001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D8001\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476BD5EC-E646-4624-B167-A6910FB08FAE}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8B058A-C13A-4FFF-8DBE-7EC3E6509285}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="7" xr2:uid="{FFAF0F3A-FACC-44CD-90E3-6CA7DF844403}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6820" activeTab="5" xr2:uid="{FFAF0F3A-FACC-44CD-90E3-6CA7DF844403}"/>
   </bookViews>
   <sheets>
     <sheet name="Today" sheetId="1" r:id="rId1"/>
@@ -18,12 +18,12 @@
     <sheet name="YearMonthDay" sheetId="3" r:id="rId3"/>
     <sheet name="EDate" sheetId="5" r:id="rId4"/>
     <sheet name="Datedif" sheetId="6" r:id="rId5"/>
-    <sheet name="Chart2" sheetId="9" r:id="rId6"/>
-    <sheet name="Chart1" sheetId="8" r:id="rId7"/>
-    <sheet name="AgeCalculation" sheetId="7" r:id="rId8"/>
+    <sheet name="AgeCalculation" sheetId="7" r:id="rId6"/>
+    <sheet name="Chart2" sheetId="9" r:id="rId7"/>
+    <sheet name="Chart1" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">AgeCalculation!$H$1:$H$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">AgeCalculation!$H$1:$H$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">YearMonthDay!$A$1:$E$54</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
@@ -2948,7 +2948,7 @@
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" s="6">
         <f ca="1">NOW()</f>
-        <v>46296.479978819443</v>
+        <v>46296.748066550928</v>
       </c>
     </row>
   </sheetData>
@@ -3644,7 +3644,7 @@
         <v>36721</v>
       </c>
       <c r="C34" s="15">
-        <f t="shared" ref="C34:C65" si="3">YEAR(B34)</f>
+        <f t="shared" ref="C34:C54" si="3">YEAR(B34)</f>
         <v>2000</v>
       </c>
       <c r="D34" s="13">
